--- a/Code/Jupiter/Connect4/Logs/PPO/PPO-2000-PPO-L-True-SP_FINALE-PPO_845 - at-2026-04-17 10-56-03-benchmark.xlsx
+++ b/Code/Jupiter/Connect4/Logs/PPO/PPO-2000-PPO-L-True-SP_FINALE-PPO_845 - at-2026-04-17 10-56-03-benchmark.xlsx
@@ -431,7 +431,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T65"/>
+  <dimension ref="A1:T102"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:20">
@@ -498,25 +498,25 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2">
-        <v>1</v>
+        <v>640</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>0.031727540625</v>
       </c>
       <c r="C2">
-        <v>0.5</v>
+        <v>0.2575</v>
       </c>
       <c r="D2">
-        <v>0.4875</v>
+        <v>0.48</v>
       </c>
       <c r="E2">
-        <v>0.9709095434461854</v>
+        <v>0.970966065241133</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>0.996875</v>
       </c>
       <c r="H2">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="I2">
         <v>1</v>
@@ -557,25 +557,25 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3">
-        <v>20</v>
+        <v>660</v>
       </c>
       <c r="B3">
-        <v>0.121875</v>
+        <v>0.0317305545454545</v>
       </c>
       <c r="C3">
-        <v>0.5</v>
+        <v>0.2575</v>
       </c>
       <c r="D3">
-        <v>0.4875</v>
+        <v>0.48</v>
       </c>
       <c r="E3">
-        <v>0.9709095434461854</v>
+        <v>0.970966065241133</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>0.996969696969697</v>
       </c>
       <c r="H3">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -616,25 +616,25 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4">
-        <v>40</v>
+        <v>720</v>
       </c>
       <c r="B4">
-        <v>0.12125</v>
+        <v>0.0317385916666667</v>
       </c>
       <c r="C4">
-        <v>0.5</v>
+        <v>0.2575</v>
       </c>
       <c r="D4">
-        <v>0.485</v>
+        <v>0.48</v>
       </c>
       <c r="E4">
-        <v>0.6907799884551348</v>
+        <v>0.970966065241133</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>0.997222222222222</v>
       </c>
       <c r="H4">
-        <v>0.995</v>
+        <v>1</v>
       </c>
       <c r="I4">
         <v>1</v>
@@ -646,16 +646,16 @@
         <v>0.5</v>
       </c>
       <c r="L4">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M4">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N4">
         <v>0.5</v>
       </c>
       <c r="O4">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="P4">
         <v>1</v>
@@ -664,7 +664,7 @@
         <v>1</v>
       </c>
       <c r="R4">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="S4">
         <v>1</v>
@@ -675,25 +675,25 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5">
-        <v>60</v>
+        <v>780</v>
       </c>
       <c r="B5">
-        <v>0.12125</v>
+        <v>0.0329901923076923</v>
       </c>
       <c r="C5">
-        <v>0.5</v>
+        <v>0.2625</v>
       </c>
       <c r="D5">
-        <v>0.485</v>
+        <v>0.48</v>
       </c>
       <c r="E5">
-        <v>0.6907799884551348</v>
+        <v>0.970966065241133</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>0.997435897435897</v>
       </c>
       <c r="H5">
-        <v>0.995</v>
+        <v>1</v>
       </c>
       <c r="I5">
         <v>1</v>
@@ -705,16 +705,16 @@
         <v>0.5</v>
       </c>
       <c r="L5">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M5">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N5">
         <v>0.5</v>
       </c>
       <c r="O5">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="P5">
         <v>1</v>
@@ -723,7 +723,7 @@
         <v>1</v>
       </c>
       <c r="R5">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="S5">
         <v>1</v>
@@ -734,25 +734,25 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6">
-        <v>80</v>
+        <v>800</v>
       </c>
       <c r="B6">
-        <v>0.12125</v>
+        <v>0.0329923125</v>
       </c>
       <c r="C6">
-        <v>0.5</v>
+        <v>0.2625</v>
       </c>
       <c r="D6">
-        <v>0.485</v>
+        <v>0.48</v>
       </c>
       <c r="E6">
-        <v>0.9258628304394209</v>
+        <v>0.970966065241133</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="H6">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="I6">
         <v>1</v>
@@ -767,13 +767,13 @@
         <v>1</v>
       </c>
       <c r="M6">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N6">
         <v>0.5</v>
       </c>
       <c r="O6">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="P6">
         <v>1</v>
@@ -793,25 +793,25 @@
     </row>
     <row r="7" spans="1:20">
       <c r="A7">
-        <v>100</v>
+        <v>520</v>
       </c>
       <c r="B7">
-        <v>0.12125</v>
+        <v>0.0317045884615385</v>
       </c>
       <c r="C7">
-        <v>0.5</v>
+        <v>0.2575</v>
       </c>
       <c r="D7">
-        <v>0.485</v>
+        <v>0.48</v>
       </c>
       <c r="E7">
-        <v>0.9258910913368946</v>
+        <v>0.970937804343659</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>0.9961538461538459</v>
       </c>
       <c r="H7">
-        <v>0.985</v>
+        <v>0.995</v>
       </c>
       <c r="I7">
         <v>1</v>
@@ -826,13 +826,13 @@
         <v>1</v>
       </c>
       <c r="M7">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N7">
         <v>0.5</v>
       </c>
       <c r="O7">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="P7">
         <v>1</v>
@@ -852,25 +852,25 @@
     </row>
     <row r="8" spans="1:20">
       <c r="A8">
-        <v>120</v>
+        <v>700</v>
       </c>
       <c r="B8">
-        <v>0.12</v>
+        <v>0.0317360657142857</v>
       </c>
       <c r="C8">
-        <v>0.5</v>
+        <v>0.2575</v>
       </c>
       <c r="D8">
         <v>0.48</v>
       </c>
       <c r="E8">
-        <v>0.9258910913368946</v>
+        <v>0.970937804343659</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>0.997142857142857</v>
       </c>
       <c r="H8">
-        <v>0.985</v>
+        <v>0.995</v>
       </c>
       <c r="I8">
         <v>1</v>
@@ -885,13 +885,13 @@
         <v>1</v>
       </c>
       <c r="M8">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N8">
         <v>0.5</v>
       </c>
       <c r="O8">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="P8">
         <v>1</v>
@@ -911,25 +911,25 @@
     </row>
     <row r="9" spans="1:20">
       <c r="A9">
-        <v>140</v>
+        <v>900</v>
       </c>
       <c r="B9">
-        <v>0.12</v>
+        <v>0.0330015</v>
       </c>
       <c r="C9">
-        <v>0.5</v>
+        <v>0.2625</v>
       </c>
       <c r="D9">
         <v>0.48</v>
       </c>
       <c r="E9">
-        <v>0.9259758740293159</v>
+        <v>0.970937804343659</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>0.997777777777778</v>
       </c>
       <c r="H9">
-        <v>1</v>
+        <v>0.995</v>
       </c>
       <c r="I9">
         <v>1</v>
@@ -944,13 +944,13 @@
         <v>1</v>
       </c>
       <c r="M9">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N9">
         <v>0.5</v>
       </c>
       <c r="O9">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="P9">
         <v>1</v>
@@ -970,25 +970,25 @@
     </row>
     <row r="10" spans="1:20">
       <c r="A10">
-        <v>160</v>
+        <v>1460</v>
       </c>
       <c r="B10">
-        <v>0.12</v>
+        <v>0.117289775342466</v>
       </c>
       <c r="C10">
-        <v>0.5</v>
+        <v>0.495</v>
       </c>
       <c r="D10">
         <v>0.48</v>
       </c>
       <c r="E10">
-        <v>0.9259758740293159</v>
+        <v>0.970937804343659</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>0.997260273972603</v>
       </c>
       <c r="H10">
-        <v>1</v>
+        <v>0.995</v>
       </c>
       <c r="I10">
         <v>1</v>
@@ -1003,13 +1003,13 @@
         <v>1</v>
       </c>
       <c r="M10">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N10">
         <v>0.5</v>
       </c>
       <c r="O10">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="P10">
         <v>1</v>
@@ -1029,25 +1029,25 @@
     </row>
     <row r="11" spans="1:20">
       <c r="A11">
-        <v>180</v>
+        <v>1</v>
       </c>
       <c r="B11">
-        <v>0.118803</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <v>0.4975</v>
+        <v>0.5</v>
       </c>
       <c r="D11">
-        <v>0.48</v>
+        <v>0.4875</v>
       </c>
       <c r="E11">
-        <v>0.9259476131318422</v>
+        <v>0.970909543446185</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11">
-        <v>0.995</v>
+        <v>0.99</v>
       </c>
       <c r="I11">
         <v>1</v>
@@ -1062,13 +1062,13 @@
         <v>1</v>
       </c>
       <c r="M11">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N11">
         <v>0.5</v>
       </c>
       <c r="O11">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="P11">
         <v>1</v>
@@ -1088,25 +1088,25 @@
     </row>
     <row r="12" spans="1:20">
       <c r="A12">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="B12">
-        <v>0.118803</v>
+        <v>0.121875</v>
       </c>
       <c r="C12">
-        <v>0.4975</v>
+        <v>0.5</v>
       </c>
       <c r="D12">
-        <v>0.48</v>
+        <v>0.4875</v>
       </c>
       <c r="E12">
-        <v>0.9258910913368946</v>
+        <v>0.970909543446185</v>
       </c>
       <c r="G12">
         <v>1</v>
       </c>
       <c r="H12">
-        <v>0.985</v>
+        <v>0.99</v>
       </c>
       <c r="I12">
         <v>1</v>
@@ -1121,13 +1121,13 @@
         <v>1</v>
       </c>
       <c r="M12">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N12">
         <v>0.5</v>
       </c>
       <c r="O12">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="P12">
         <v>1</v>
@@ -1147,22 +1147,22 @@
     </row>
     <row r="13" spans="1:20">
       <c r="A13">
-        <v>220</v>
+        <v>940</v>
       </c>
       <c r="B13">
-        <v>0.118803</v>
+        <v>0.0330046276595745</v>
       </c>
       <c r="C13">
-        <v>0.4975</v>
+        <v>0.2625</v>
       </c>
       <c r="D13">
         <v>0.48</v>
       </c>
       <c r="E13">
-        <v>0.9259193522343683</v>
+        <v>0.970909543446185</v>
       </c>
       <c r="G13">
-        <v>1</v>
+        <v>0.997872340425532</v>
       </c>
       <c r="H13">
         <v>0.99</v>
@@ -1180,13 +1180,13 @@
         <v>1</v>
       </c>
       <c r="M13">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N13">
         <v>0.5</v>
       </c>
       <c r="O13">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="P13">
         <v>1</v>
@@ -1206,25 +1206,25 @@
     </row>
     <row r="14" spans="1:20">
       <c r="A14">
-        <v>240</v>
+        <v>1440</v>
       </c>
       <c r="B14">
-        <v>0.118803</v>
+        <v>0.1172853</v>
       </c>
       <c r="C14">
-        <v>0.4975</v>
+        <v>0.495</v>
       </c>
       <c r="D14">
         <v>0.48</v>
       </c>
       <c r="E14">
-        <v>0.9259476131318422</v>
+        <v>0.970909543446185</v>
       </c>
       <c r="G14">
-        <v>1</v>
+        <v>0.997222222222222</v>
       </c>
       <c r="H14">
-        <v>0.995</v>
+        <v>0.99</v>
       </c>
       <c r="I14">
         <v>1</v>
@@ -1239,13 +1239,13 @@
         <v>1</v>
       </c>
       <c r="M14">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N14">
         <v>0.5</v>
       </c>
       <c r="O14">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="P14">
         <v>1</v>
@@ -1265,25 +1265,25 @@
     </row>
     <row r="15" spans="1:20">
       <c r="A15">
-        <v>260</v>
+        <v>500</v>
       </c>
       <c r="B15">
-        <v>0.032617</v>
+        <v>0.031699692</v>
       </c>
       <c r="C15">
-        <v>0.26</v>
+        <v>0.2575</v>
       </c>
       <c r="D15">
-        <v>0.4825</v>
+        <v>0.48</v>
       </c>
       <c r="E15">
-        <v>0.9259758740293159</v>
+        <v>0.970881282548712</v>
       </c>
       <c r="G15">
-        <v>1</v>
+        <v>0.996</v>
       </c>
       <c r="H15">
-        <v>1</v>
+        <v>0.985</v>
       </c>
       <c r="I15">
         <v>1</v>
@@ -1298,13 +1298,13 @@
         <v>1</v>
       </c>
       <c r="M15">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N15">
         <v>0.5</v>
       </c>
       <c r="O15">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="P15">
         <v>1</v>
@@ -1324,25 +1324,25 @@
     </row>
     <row r="16" spans="1:20">
       <c r="A16">
-        <v>280</v>
+        <v>540</v>
       </c>
       <c r="B16">
-        <v>0.032617</v>
+        <v>0.0317091222222222</v>
       </c>
       <c r="C16">
-        <v>0.26</v>
+        <v>0.2575</v>
       </c>
       <c r="D16">
-        <v>0.4825</v>
+        <v>0.48</v>
       </c>
       <c r="E16">
-        <v>0.9259758740293159</v>
+        <v>0.970853021651238</v>
       </c>
       <c r="G16">
-        <v>1</v>
+        <v>0.996296296296296</v>
       </c>
       <c r="H16">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="I16">
         <v>1</v>
@@ -1357,13 +1357,13 @@
         <v>1</v>
       </c>
       <c r="M16">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N16">
         <v>0.5</v>
       </c>
       <c r="O16">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="P16">
         <v>1</v>
@@ -1383,25 +1383,25 @@
     </row>
     <row r="17" spans="1:20">
       <c r="A17">
-        <v>300</v>
+        <v>920</v>
       </c>
       <c r="B17">
-        <v>0.03215853125</v>
+        <v>0.033003097826087</v>
       </c>
       <c r="C17">
-        <v>0.2575</v>
+        <v>0.2625</v>
       </c>
       <c r="D17">
-        <v>0.485</v>
+        <v>0.48</v>
       </c>
       <c r="E17">
-        <v>0.9259758740293159</v>
+        <v>0.970853021651238</v>
       </c>
       <c r="G17">
-        <v>1</v>
+        <v>0.997826086956522</v>
       </c>
       <c r="H17">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="I17">
         <v>1</v>
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="M17">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N17">
         <v>0.5</v>
       </c>
       <c r="O17">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="P17">
         <v>1</v>
@@ -1442,22 +1442,22 @@
     </row>
     <row r="18" spans="1:20">
       <c r="A18">
-        <v>320</v>
+        <v>740</v>
       </c>
       <c r="B18">
-        <v>0.03215853125</v>
+        <v>0.0329856081081081</v>
       </c>
       <c r="C18">
-        <v>0.2575</v>
+        <v>0.2625</v>
       </c>
       <c r="D18">
-        <v>0.485</v>
+        <v>0.48</v>
       </c>
       <c r="E18">
-        <v>0.9259758740293159</v>
+        <v>0.965426929336282</v>
       </c>
       <c r="G18">
-        <v>1</v>
+        <v>0.997297297297297</v>
       </c>
       <c r="H18">
         <v>1</v>
@@ -1466,7 +1466,7 @@
         <v>1</v>
       </c>
       <c r="J18">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K18">
         <v>0.5</v>
@@ -1475,13 +1475,13 @@
         <v>1</v>
       </c>
       <c r="M18">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N18">
         <v>0.5</v>
       </c>
       <c r="O18">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="P18">
         <v>1</v>
@@ -1501,31 +1501,31 @@
     </row>
     <row r="19" spans="1:20">
       <c r="A19">
-        <v>340</v>
+        <v>680</v>
       </c>
       <c r="B19">
-        <v>0.03215853125</v>
+        <v>0.0317333911764706</v>
       </c>
       <c r="C19">
         <v>0.2575</v>
       </c>
       <c r="D19">
-        <v>0.485</v>
+        <v>0.48</v>
       </c>
       <c r="E19">
-        <v>0.9258910913368946</v>
+        <v>0.965370407541334</v>
       </c>
       <c r="G19">
-        <v>1</v>
+        <v>0.997058823529412</v>
       </c>
       <c r="H19">
-        <v>0.985</v>
+        <v>0.99</v>
       </c>
       <c r="I19">
         <v>1</v>
       </c>
       <c r="J19">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K19">
         <v>0.5</v>
@@ -1534,13 +1534,13 @@
         <v>1</v>
       </c>
       <c r="M19">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N19">
         <v>0.5</v>
       </c>
       <c r="O19">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="P19">
         <v>1</v>
@@ -1560,31 +1560,31 @@
     </row>
     <row r="20" spans="1:20">
       <c r="A20">
-        <v>360</v>
+        <v>760</v>
       </c>
       <c r="B20">
-        <v>0.03306255859375</v>
+        <v>0.0329879605263158</v>
       </c>
       <c r="C20">
         <v>0.2625</v>
       </c>
       <c r="D20">
-        <v>0.4825</v>
+        <v>0.48</v>
       </c>
       <c r="E20">
-        <v>0.9259476131318422</v>
+        <v>0.965285624848913</v>
       </c>
       <c r="G20">
-        <v>0.9944444444444445</v>
+        <v>0.997368421052632</v>
       </c>
       <c r="H20">
-        <v>0.995</v>
+        <v>0.975</v>
       </c>
       <c r="I20">
         <v>1</v>
       </c>
       <c r="J20">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K20">
         <v>0.5</v>
@@ -1593,13 +1593,13 @@
         <v>1</v>
       </c>
       <c r="M20">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N20">
         <v>0.5</v>
       </c>
       <c r="O20">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="P20">
         <v>1</v>
@@ -1619,25 +1619,25 @@
     </row>
     <row r="21" spans="1:20">
       <c r="A21">
-        <v>380</v>
+        <v>960</v>
       </c>
       <c r="B21">
-        <v>0.03307228001644737</v>
+        <v>0.03176069375</v>
       </c>
       <c r="C21">
-        <v>0.2625</v>
+        <v>0.2575</v>
       </c>
       <c r="D21">
-        <v>0.4825</v>
+        <v>0.48</v>
       </c>
       <c r="E21">
-        <v>0.9259758740293159</v>
+        <v>0.949658659851584</v>
       </c>
       <c r="G21">
-        <v>0.9947368421052631</v>
+        <v>0.997916666666667</v>
       </c>
       <c r="H21">
-        <v>1</v>
+        <v>0.995</v>
       </c>
       <c r="I21">
         <v>1</v>
@@ -1652,13 +1652,13 @@
         <v>1</v>
       </c>
       <c r="M21">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N21">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="O21">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="P21">
         <v>1</v>
@@ -1678,22 +1678,22 @@
     </row>
     <row r="22" spans="1:20">
       <c r="A22">
-        <v>400</v>
+        <v>980</v>
       </c>
       <c r="B22">
-        <v>0.032909625</v>
+        <v>0.0317620469387755</v>
       </c>
       <c r="C22">
-        <v>0.2625</v>
+        <v>0.2575</v>
       </c>
       <c r="D22">
         <v>0.48</v>
       </c>
       <c r="E22">
-        <v>0.9259476131318422</v>
+        <v>0.949658659851584</v>
       </c>
       <c r="G22">
-        <v>0.995</v>
+        <v>0.997959183673469</v>
       </c>
       <c r="H22">
         <v>0.995</v>
@@ -1711,13 +1711,13 @@
         <v>1</v>
       </c>
       <c r="M22">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N22">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="O22">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="P22">
         <v>1</v>
@@ -1737,25 +1737,25 @@
     </row>
     <row r="23" spans="1:20">
       <c r="A23">
-        <v>420</v>
+        <v>140</v>
       </c>
       <c r="B23">
-        <v>0.0329175</v>
+        <v>0.12</v>
       </c>
       <c r="C23">
-        <v>0.2625</v>
+        <v>0.5</v>
       </c>
       <c r="D23">
         <v>0.48</v>
       </c>
       <c r="E23">
-        <v>0.9258910913368946</v>
+        <v>0.925975874029316</v>
       </c>
       <c r="G23">
-        <v>0.9952380952380953</v>
+        <v>1</v>
       </c>
       <c r="H23">
-        <v>0.985</v>
+        <v>1</v>
       </c>
       <c r="I23">
         <v>1</v>
@@ -1796,25 +1796,25 @@
     </row>
     <row r="24" spans="1:20">
       <c r="A24">
-        <v>440</v>
+        <v>160</v>
       </c>
       <c r="B24">
-        <v>0.03292465909090909</v>
+        <v>0.12</v>
       </c>
       <c r="C24">
-        <v>0.2625</v>
+        <v>0.5</v>
       </c>
       <c r="D24">
         <v>0.48</v>
       </c>
       <c r="E24">
-        <v>0.9259476131318422</v>
+        <v>0.925975874029316</v>
       </c>
       <c r="G24">
-        <v>0.9954545454545455</v>
+        <v>1</v>
       </c>
       <c r="H24">
-        <v>0.995</v>
+        <v>1</v>
       </c>
       <c r="I24">
         <v>1</v>
@@ -1855,25 +1855,25 @@
     </row>
     <row r="25" spans="1:20">
       <c r="A25">
-        <v>460</v>
+        <v>260</v>
       </c>
       <c r="B25">
-        <v>0.03185366664402173</v>
+        <v>0.032617</v>
       </c>
       <c r="C25">
-        <v>0.2575</v>
+        <v>0.26</v>
       </c>
       <c r="D25">
         <v>0.4825</v>
       </c>
       <c r="E25">
-        <v>0.9258628304394209</v>
+        <v>0.925975874029316</v>
       </c>
       <c r="G25">
-        <v>0.9956521739130435</v>
+        <v>1</v>
       </c>
       <c r="H25">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="I25">
         <v>1</v>
@@ -1914,25 +1914,25 @@
     </row>
     <row r="26" spans="1:20">
       <c r="A26">
-        <v>480</v>
+        <v>280</v>
       </c>
       <c r="B26">
-        <v>0.03185946243489583</v>
+        <v>0.032617</v>
       </c>
       <c r="C26">
-        <v>0.2575</v>
+        <v>0.26</v>
       </c>
       <c r="D26">
         <v>0.4825</v>
       </c>
       <c r="E26">
-        <v>0.9259476131318422</v>
+        <v>0.925975874029316</v>
       </c>
       <c r="G26">
-        <v>0.9958333333333333</v>
+        <v>1</v>
       </c>
       <c r="H26">
-        <v>0.995</v>
+        <v>1</v>
       </c>
       <c r="I26">
         <v>1</v>
@@ -1973,25 +1973,25 @@
     </row>
     <row r="27" spans="1:20">
       <c r="A27">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="B27">
-        <v>0.03169969199999999</v>
+        <v>0.03215853125</v>
       </c>
       <c r="C27">
         <v>0.2575</v>
       </c>
       <c r="D27">
-        <v>0.48</v>
+        <v>0.485</v>
       </c>
       <c r="E27">
-        <v>0.9708812825487118</v>
+        <v>0.925975874029316</v>
       </c>
       <c r="G27">
-        <v>0.996</v>
+        <v>1</v>
       </c>
       <c r="H27">
-        <v>0.985</v>
+        <v>1</v>
       </c>
       <c r="I27">
         <v>1</v>
@@ -2006,13 +2006,13 @@
         <v>1</v>
       </c>
       <c r="M27">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="N27">
         <v>0.5</v>
       </c>
       <c r="O27">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="P27">
         <v>1</v>
@@ -2032,25 +2032,25 @@
     </row>
     <row r="28" spans="1:20">
       <c r="A28">
-        <v>520</v>
+        <v>320</v>
       </c>
       <c r="B28">
-        <v>0.03170458846153846</v>
+        <v>0.03215853125</v>
       </c>
       <c r="C28">
         <v>0.2575</v>
       </c>
       <c r="D28">
-        <v>0.48</v>
+        <v>0.485</v>
       </c>
       <c r="E28">
-        <v>0.9709378043436592</v>
+        <v>0.925975874029316</v>
       </c>
       <c r="G28">
-        <v>0.9961538461538462</v>
+        <v>1</v>
       </c>
       <c r="H28">
-        <v>0.995</v>
+        <v>1</v>
       </c>
       <c r="I28">
         <v>1</v>
@@ -2065,13 +2065,13 @@
         <v>1</v>
       </c>
       <c r="M28">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="N28">
         <v>0.5</v>
       </c>
       <c r="O28">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="P28">
         <v>1</v>
@@ -2091,25 +2091,25 @@
     </row>
     <row r="29" spans="1:20">
       <c r="A29">
-        <v>540</v>
+        <v>380</v>
       </c>
       <c r="B29">
-        <v>0.03170912222222222</v>
+        <v>0.0330722800164474</v>
       </c>
       <c r="C29">
-        <v>0.2575</v>
+        <v>0.2625</v>
       </c>
       <c r="D29">
-        <v>0.48</v>
+        <v>0.4825</v>
       </c>
       <c r="E29">
-        <v>0.970853021651238</v>
+        <v>0.925975874029316</v>
       </c>
       <c r="G29">
-        <v>0.9962962962962963</v>
+        <v>0.994736842105263</v>
       </c>
       <c r="H29">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="I29">
         <v>1</v>
@@ -2124,13 +2124,13 @@
         <v>1</v>
       </c>
       <c r="M29">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="N29">
         <v>0.5</v>
       </c>
       <c r="O29">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="P29">
         <v>1</v>
@@ -2150,25 +2150,25 @@
     </row>
     <row r="30" spans="1:20">
       <c r="A30">
-        <v>560</v>
+        <v>180</v>
       </c>
       <c r="B30">
-        <v>0.03171333214285714</v>
+        <v>0.118803</v>
       </c>
       <c r="C30">
-        <v>0.2575</v>
+        <v>0.4975</v>
       </c>
       <c r="D30">
         <v>0.48</v>
       </c>
       <c r="E30">
-        <v>0.7357419187694781</v>
+        <v>0.925947613131842</v>
       </c>
       <c r="G30">
-        <v>0.9964285714285714</v>
+        <v>1</v>
       </c>
       <c r="H30">
-        <v>0.99</v>
+        <v>0.995</v>
       </c>
       <c r="I30">
         <v>1</v>
@@ -2180,16 +2180,16 @@
         <v>0.5</v>
       </c>
       <c r="L30">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M30">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="N30">
         <v>0.5</v>
       </c>
       <c r="O30">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="P30">
         <v>1</v>
@@ -2198,7 +2198,7 @@
         <v>1</v>
       </c>
       <c r="R30">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="S30">
         <v>1</v>
@@ -2209,25 +2209,25 @@
     </row>
     <row r="31" spans="1:20">
       <c r="A31">
-        <v>580</v>
+        <v>240</v>
       </c>
       <c r="B31">
-        <v>0.03171725172413793</v>
+        <v>0.118803</v>
       </c>
       <c r="C31">
-        <v>0.2575</v>
+        <v>0.4975</v>
       </c>
       <c r="D31">
         <v>0.48</v>
       </c>
       <c r="E31">
-        <v>0.7357419187694781</v>
+        <v>0.925947613131842</v>
       </c>
       <c r="G31">
-        <v>0.996551724137931</v>
+        <v>1</v>
       </c>
       <c r="H31">
-        <v>0.99</v>
+        <v>0.995</v>
       </c>
       <c r="I31">
         <v>1</v>
@@ -2239,16 +2239,16 @@
         <v>0.5</v>
       </c>
       <c r="L31">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M31">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="N31">
         <v>0.5</v>
       </c>
       <c r="O31">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="P31">
         <v>1</v>
@@ -2257,7 +2257,7 @@
         <v>1</v>
       </c>
       <c r="R31">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="S31">
         <v>1</v>
@@ -2268,46 +2268,46 @@
     </row>
     <row r="32" spans="1:20">
       <c r="A32">
-        <v>600</v>
+        <v>360</v>
       </c>
       <c r="B32">
-        <v>0.03172091</v>
+        <v>0.03306255859375</v>
       </c>
       <c r="C32">
-        <v>0.2575</v>
+        <v>0.2625</v>
       </c>
       <c r="D32">
-        <v>0.48</v>
+        <v>0.4825</v>
       </c>
       <c r="E32">
-        <v>0.730202782864627</v>
+        <v>0.925947613131842</v>
       </c>
       <c r="G32">
-        <v>0.9966666666666667</v>
+        <v>0.994444444444445</v>
       </c>
       <c r="H32">
-        <v>0.99</v>
+        <v>0.995</v>
       </c>
       <c r="I32">
         <v>1</v>
       </c>
       <c r="J32">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K32">
         <v>0.5</v>
       </c>
       <c r="L32">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M32">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="N32">
         <v>0.5</v>
       </c>
       <c r="O32">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="P32">
         <v>1</v>
@@ -2316,7 +2316,7 @@
         <v>1</v>
       </c>
       <c r="R32">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="S32">
         <v>1</v>
@@ -2327,46 +2327,46 @@
     </row>
     <row r="33" spans="1:20">
       <c r="A33">
-        <v>620</v>
+        <v>400</v>
       </c>
       <c r="B33">
-        <v>0.03172433225806452</v>
+        <v>0.032909625</v>
       </c>
       <c r="C33">
-        <v>0.2575</v>
+        <v>0.2625</v>
       </c>
       <c r="D33">
         <v>0.48</v>
       </c>
       <c r="E33">
-        <v>0.7301745219671534</v>
+        <v>0.925947613131842</v>
       </c>
       <c r="G33">
-        <v>0.9967741935483871</v>
+        <v>0.995</v>
       </c>
       <c r="H33">
-        <v>0.985</v>
+        <v>0.995</v>
       </c>
       <c r="I33">
         <v>1</v>
       </c>
       <c r="J33">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K33">
         <v>0.5</v>
       </c>
       <c r="L33">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M33">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="N33">
         <v>0.5</v>
       </c>
       <c r="O33">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="P33">
         <v>1</v>
@@ -2375,7 +2375,7 @@
         <v>1</v>
       </c>
       <c r="R33">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="S33">
         <v>1</v>
@@ -2386,25 +2386,25 @@
     </row>
     <row r="34" spans="1:20">
       <c r="A34">
-        <v>640</v>
+        <v>440</v>
       </c>
       <c r="B34">
-        <v>0.03172754062499999</v>
+        <v>0.0329246590909091</v>
       </c>
       <c r="C34">
-        <v>0.2575</v>
+        <v>0.2625</v>
       </c>
       <c r="D34">
         <v>0.48</v>
       </c>
       <c r="E34">
-        <v>0.9709660652411329</v>
+        <v>0.925947613131842</v>
       </c>
       <c r="G34">
-        <v>0.996875</v>
+        <v>0.995454545454546</v>
       </c>
       <c r="H34">
-        <v>1</v>
+        <v>0.995</v>
       </c>
       <c r="I34">
         <v>1</v>
@@ -2419,13 +2419,13 @@
         <v>1</v>
       </c>
       <c r="M34">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="N34">
         <v>0.5</v>
       </c>
       <c r="O34">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="P34">
         <v>1</v>
@@ -2445,25 +2445,25 @@
     </row>
     <row r="35" spans="1:20">
       <c r="A35">
-        <v>660</v>
+        <v>480</v>
       </c>
       <c r="B35">
-        <v>0.03173055454545454</v>
+        <v>0.0318594624348958</v>
       </c>
       <c r="C35">
         <v>0.2575</v>
       </c>
       <c r="D35">
-        <v>0.48</v>
+        <v>0.4825</v>
       </c>
       <c r="E35">
-        <v>0.9709660652411329</v>
+        <v>0.925947613131842</v>
       </c>
       <c r="G35">
-        <v>0.996969696969697</v>
+        <v>0.995833333333333</v>
       </c>
       <c r="H35">
-        <v>1</v>
+        <v>0.995</v>
       </c>
       <c r="I35">
         <v>1</v>
@@ -2478,13 +2478,13 @@
         <v>1</v>
       </c>
       <c r="M35">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="N35">
         <v>0.5</v>
       </c>
       <c r="O35">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="P35">
         <v>1</v>
@@ -2504,22 +2504,22 @@
     </row>
     <row r="36" spans="1:20">
       <c r="A36">
-        <v>680</v>
+        <v>220</v>
       </c>
       <c r="B36">
-        <v>0.03173339117647058</v>
+        <v>0.118803</v>
       </c>
       <c r="C36">
-        <v>0.2575</v>
+        <v>0.4975</v>
       </c>
       <c r="D36">
         <v>0.48</v>
       </c>
       <c r="E36">
-        <v>0.9653704075413344</v>
+        <v>0.9259193522343681</v>
       </c>
       <c r="G36">
-        <v>0.9970588235294118</v>
+        <v>1</v>
       </c>
       <c r="H36">
         <v>0.99</v>
@@ -2528,7 +2528,7 @@
         <v>1</v>
       </c>
       <c r="J36">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K36">
         <v>0.5</v>
@@ -2537,13 +2537,13 @@
         <v>1</v>
       </c>
       <c r="M36">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="N36">
         <v>0.5</v>
       </c>
       <c r="O36">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="P36">
         <v>1</v>
@@ -2563,25 +2563,25 @@
     </row>
     <row r="37" spans="1:20">
       <c r="A37">
-        <v>700</v>
+        <v>100</v>
       </c>
       <c r="B37">
-        <v>0.03173606571428571</v>
+        <v>0.12125</v>
       </c>
       <c r="C37">
-        <v>0.2575</v>
+        <v>0.5</v>
       </c>
       <c r="D37">
-        <v>0.48</v>
+        <v>0.485</v>
       </c>
       <c r="E37">
-        <v>0.9709378043436592</v>
+        <v>0.925891091336895</v>
       </c>
       <c r="G37">
-        <v>0.9971428571428571</v>
+        <v>1</v>
       </c>
       <c r="H37">
-        <v>0.995</v>
+        <v>0.985</v>
       </c>
       <c r="I37">
         <v>1</v>
@@ -2596,13 +2596,13 @@
         <v>1</v>
       </c>
       <c r="M37">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="N37">
         <v>0.5</v>
       </c>
       <c r="O37">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="P37">
         <v>1</v>
@@ -2622,25 +2622,25 @@
     </row>
     <row r="38" spans="1:20">
       <c r="A38">
-        <v>720</v>
+        <v>120</v>
       </c>
       <c r="B38">
-        <v>0.03173859166666666</v>
+        <v>0.12</v>
       </c>
       <c r="C38">
-        <v>0.2575</v>
+        <v>0.5</v>
       </c>
       <c r="D38">
         <v>0.48</v>
       </c>
       <c r="E38">
-        <v>0.9709660652411329</v>
+        <v>0.925891091336895</v>
       </c>
       <c r="G38">
-        <v>0.9972222222222222</v>
+        <v>1</v>
       </c>
       <c r="H38">
-        <v>1</v>
+        <v>0.985</v>
       </c>
       <c r="I38">
         <v>1</v>
@@ -2655,13 +2655,13 @@
         <v>1</v>
       </c>
       <c r="M38">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="N38">
         <v>0.5</v>
       </c>
       <c r="O38">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="P38">
         <v>1</v>
@@ -2681,31 +2681,31 @@
     </row>
     <row r="39" spans="1:20">
       <c r="A39">
-        <v>740</v>
+        <v>200</v>
       </c>
       <c r="B39">
-        <v>0.03298560810810811</v>
+        <v>0.118803</v>
       </c>
       <c r="C39">
-        <v>0.2625</v>
+        <v>0.4975</v>
       </c>
       <c r="D39">
         <v>0.48</v>
       </c>
       <c r="E39">
-        <v>0.9654269293362818</v>
+        <v>0.925891091336895</v>
       </c>
       <c r="G39">
-        <v>0.9972972972972973</v>
+        <v>1</v>
       </c>
       <c r="H39">
-        <v>1</v>
+        <v>0.985</v>
       </c>
       <c r="I39">
         <v>1</v>
       </c>
       <c r="J39">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K39">
         <v>0.5</v>
@@ -2714,13 +2714,13 @@
         <v>1</v>
       </c>
       <c r="M39">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="N39">
         <v>0.5</v>
       </c>
       <c r="O39">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="P39">
         <v>1</v>
@@ -2740,31 +2740,31 @@
     </row>
     <row r="40" spans="1:20">
       <c r="A40">
-        <v>760</v>
+        <v>340</v>
       </c>
       <c r="B40">
-        <v>0.03298796052631579</v>
+        <v>0.03215853125</v>
       </c>
       <c r="C40">
-        <v>0.2625</v>
+        <v>0.2575</v>
       </c>
       <c r="D40">
-        <v>0.48</v>
+        <v>0.485</v>
       </c>
       <c r="E40">
-        <v>0.9652856248489132</v>
+        <v>0.925891091336895</v>
       </c>
       <c r="G40">
-        <v>0.9973684210526316</v>
+        <v>1</v>
       </c>
       <c r="H40">
-        <v>0.975</v>
+        <v>0.985</v>
       </c>
       <c r="I40">
         <v>1</v>
       </c>
       <c r="J40">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K40">
         <v>0.5</v>
@@ -2773,13 +2773,13 @@
         <v>1</v>
       </c>
       <c r="M40">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="N40">
         <v>0.5</v>
       </c>
       <c r="O40">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="P40">
         <v>1</v>
@@ -2799,10 +2799,10 @@
     </row>
     <row r="41" spans="1:20">
       <c r="A41">
-        <v>780</v>
+        <v>420</v>
       </c>
       <c r="B41">
-        <v>0.03299019230769231</v>
+        <v>0.0329175</v>
       </c>
       <c r="C41">
         <v>0.2625</v>
@@ -2811,13 +2811,13 @@
         <v>0.48</v>
       </c>
       <c r="E41">
-        <v>0.9709660652411329</v>
+        <v>0.925891091336895</v>
       </c>
       <c r="G41">
-        <v>0.9974358974358974</v>
+        <v>0.995238095238095</v>
       </c>
       <c r="H41">
-        <v>1</v>
+        <v>0.985</v>
       </c>
       <c r="I41">
         <v>1</v>
@@ -2832,13 +2832,13 @@
         <v>1</v>
       </c>
       <c r="M41">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="N41">
         <v>0.5</v>
       </c>
       <c r="O41">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="P41">
         <v>1</v>
@@ -2858,25 +2858,25 @@
     </row>
     <row r="42" spans="1:20">
       <c r="A42">
-        <v>800</v>
+        <v>80</v>
       </c>
       <c r="B42">
-        <v>0.0329923125</v>
+        <v>0.12125</v>
       </c>
       <c r="C42">
-        <v>0.2625</v>
+        <v>0.5</v>
       </c>
       <c r="D42">
-        <v>0.48</v>
+        <v>0.485</v>
       </c>
       <c r="E42">
-        <v>0.9709660652411329</v>
+        <v>0.925862830439421</v>
       </c>
       <c r="G42">
-        <v>0.9975000000000001</v>
+        <v>1</v>
       </c>
       <c r="H42">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="I42">
         <v>1</v>
@@ -2891,13 +2891,13 @@
         <v>1</v>
       </c>
       <c r="M42">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="N42">
         <v>0.5</v>
       </c>
       <c r="O42">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="P42">
         <v>1</v>
@@ -2917,25 +2917,25 @@
     </row>
     <row r="43" spans="1:20">
       <c r="A43">
-        <v>820</v>
+        <v>460</v>
       </c>
       <c r="B43">
-        <v>0.03299432926829268</v>
+        <v>0.0318536666440217</v>
       </c>
       <c r="C43">
-        <v>0.2625</v>
+        <v>0.2575</v>
       </c>
       <c r="D43">
-        <v>0.48</v>
+        <v>0.4825</v>
       </c>
       <c r="E43">
-        <v>0.7465986251429861</v>
+        <v>0.925862830439421</v>
       </c>
       <c r="G43">
-        <v>0.9975609756097561</v>
+        <v>0.9956521739130439</v>
       </c>
       <c r="H43">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="I43">
         <v>1</v>
@@ -2950,13 +2950,13 @@
         <v>1</v>
       </c>
       <c r="M43">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="N43">
         <v>0.5</v>
       </c>
       <c r="O43">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="P43">
         <v>1</v>
@@ -2965,7 +2965,7 @@
         <v>1</v>
       </c>
       <c r="R43">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="S43">
         <v>1</v>
@@ -2976,25 +2976,25 @@
     </row>
     <row r="44" spans="1:20">
       <c r="A44">
-        <v>840</v>
+        <v>1420</v>
       </c>
       <c r="B44">
-        <v>0.03299625</v>
+        <v>0.118468343661972</v>
       </c>
       <c r="C44">
-        <v>0.2625</v>
+        <v>0.4975</v>
       </c>
       <c r="D44">
         <v>0.48</v>
       </c>
       <c r="E44">
-        <v>0.7465986251429861</v>
+        <v>0.9125760927548771</v>
       </c>
       <c r="G44">
-        <v>0.9976190476190476</v>
+        <v>0.997183098591549</v>
       </c>
       <c r="H44">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="I44">
         <v>1</v>
@@ -3018,13 +3018,13 @@
         <v>1</v>
       </c>
       <c r="P44">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="Q44">
         <v>1</v>
       </c>
       <c r="R44">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="S44">
         <v>1</v>
@@ -3035,25 +3035,25 @@
     </row>
     <row r="45" spans="1:20">
       <c r="A45">
-        <v>860</v>
+        <v>1600</v>
       </c>
       <c r="B45">
-        <v>0.03299808139534884</v>
+        <v>0.00010773</v>
       </c>
       <c r="C45">
-        <v>0.2625</v>
+        <v>0.015</v>
       </c>
       <c r="D45">
         <v>0.48</v>
       </c>
       <c r="E45">
-        <v>0.7357419187694781</v>
+        <v>0.9125760927548771</v>
       </c>
       <c r="G45">
-        <v>0.9976744186046511</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="H45">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="I45">
         <v>1</v>
@@ -3065,7 +3065,7 @@
         <v>0.5</v>
       </c>
       <c r="L45">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M45">
         <v>1</v>
@@ -3077,13 +3077,13 @@
         <v>1</v>
       </c>
       <c r="P45">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="Q45">
         <v>1</v>
       </c>
       <c r="R45">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="S45">
         <v>1</v>
@@ -3094,25 +3094,25 @@
     </row>
     <row r="46" spans="1:20">
       <c r="A46">
-        <v>880</v>
+        <v>1520</v>
       </c>
       <c r="B46">
-        <v>0.03299982954545454</v>
+        <v>0.117302494736842</v>
       </c>
       <c r="C46">
-        <v>0.2625</v>
+        <v>0.495</v>
       </c>
       <c r="D46">
         <v>0.48</v>
       </c>
       <c r="E46">
-        <v>0.7357136578720045</v>
+        <v>0.912547831857404</v>
       </c>
       <c r="G46">
-        <v>0.9977272727272727</v>
+        <v>0.997368421052632</v>
       </c>
       <c r="H46">
-        <v>0.985</v>
+        <v>0.995</v>
       </c>
       <c r="I46">
         <v>1</v>
@@ -3124,7 +3124,7 @@
         <v>0.5</v>
       </c>
       <c r="L46">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M46">
         <v>1</v>
@@ -3136,13 +3136,13 @@
         <v>1</v>
       </c>
       <c r="P46">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="Q46">
         <v>1</v>
       </c>
       <c r="R46">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="S46">
         <v>1</v>
@@ -3153,22 +3153,22 @@
     </row>
     <row r="47" spans="1:20">
       <c r="A47">
-        <v>900</v>
+        <v>1540</v>
       </c>
       <c r="B47">
-        <v>0.0330015</v>
+        <v>0.117306514285714</v>
       </c>
       <c r="C47">
-        <v>0.2625</v>
+        <v>0.495</v>
       </c>
       <c r="D47">
         <v>0.48</v>
       </c>
       <c r="E47">
-        <v>0.9709378043436592</v>
+        <v>0.912547831857404</v>
       </c>
       <c r="G47">
-        <v>0.9977777777777778</v>
+        <v>0.997402597402597</v>
       </c>
       <c r="H47">
         <v>0.995</v>
@@ -3195,7 +3195,7 @@
         <v>1</v>
       </c>
       <c r="P47">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="Q47">
         <v>1</v>
@@ -3212,25 +3212,25 @@
     </row>
     <row r="48" spans="1:20">
       <c r="A48">
-        <v>920</v>
+        <v>1560</v>
       </c>
       <c r="B48">
-        <v>0.03300309782608696</v>
+        <v>0.000107723076923077</v>
       </c>
       <c r="C48">
-        <v>0.2625</v>
+        <v>0.015</v>
       </c>
       <c r="D48">
         <v>0.48</v>
       </c>
       <c r="E48">
-        <v>0.970853021651238</v>
+        <v>0.912547831857404</v>
       </c>
       <c r="G48">
-        <v>0.9978260869565218</v>
+        <v>0.997435897435897</v>
       </c>
       <c r="H48">
-        <v>0.98</v>
+        <v>0.995</v>
       </c>
       <c r="I48">
         <v>1</v>
@@ -3254,7 +3254,7 @@
         <v>1</v>
       </c>
       <c r="P48">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="Q48">
         <v>1</v>
@@ -3271,25 +3271,25 @@
     </row>
     <row r="49" spans="1:20">
       <c r="A49">
-        <v>940</v>
+        <v>1620</v>
       </c>
       <c r="B49">
-        <v>0.03300462765957447</v>
+        <v>0.1185437</v>
       </c>
       <c r="C49">
-        <v>0.2625</v>
+        <v>0.495</v>
       </c>
       <c r="D49">
-        <v>0.48</v>
+        <v>0.485</v>
       </c>
       <c r="E49">
-        <v>0.9709095434461854</v>
+        <v>0.912547831857404</v>
       </c>
       <c r="G49">
-        <v>0.997872340425532</v>
+        <v>0.997530864197531</v>
       </c>
       <c r="H49">
-        <v>0.99</v>
+        <v>0.995</v>
       </c>
       <c r="I49">
         <v>1</v>
@@ -3313,7 +3313,7 @@
         <v>1</v>
       </c>
       <c r="P49">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="Q49">
         <v>1</v>
@@ -3330,22 +3330,22 @@
     </row>
     <row r="50" spans="1:20">
       <c r="A50">
-        <v>960</v>
+        <v>1640</v>
       </c>
       <c r="B50">
-        <v>0.03176069374999999</v>
+        <v>0.118547278353659</v>
       </c>
       <c r="C50">
-        <v>0.2575</v>
+        <v>0.495</v>
       </c>
       <c r="D50">
-        <v>0.48</v>
+        <v>0.485</v>
       </c>
       <c r="E50">
-        <v>0.9496586598515836</v>
+        <v>0.912547831857404</v>
       </c>
       <c r="G50">
-        <v>0.9979166666666667</v>
+        <v>0.997560975609756</v>
       </c>
       <c r="H50">
         <v>0.995</v>
@@ -3366,13 +3366,13 @@
         <v>1</v>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="O50">
         <v>1</v>
       </c>
       <c r="P50">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="Q50">
         <v>1</v>
@@ -3389,25 +3389,25 @@
     </row>
     <row r="51" spans="1:20">
       <c r="A51">
-        <v>980</v>
+        <v>1580</v>
       </c>
       <c r="B51">
-        <v>0.0317620469387755</v>
+        <v>0.000107726582278481</v>
       </c>
       <c r="C51">
-        <v>0.2575</v>
+        <v>0.015</v>
       </c>
       <c r="D51">
         <v>0.48</v>
       </c>
       <c r="E51">
-        <v>0.9496586598515836</v>
+        <v>0.912491310062456</v>
       </c>
       <c r="G51">
-        <v>0.9979591836734694</v>
+        <v>0.99746835443038</v>
       </c>
       <c r="H51">
-        <v>0.995</v>
+        <v>0.985</v>
       </c>
       <c r="I51">
         <v>1</v>
@@ -3425,13 +3425,13 @@
         <v>1</v>
       </c>
       <c r="N51">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="O51">
         <v>1</v>
       </c>
       <c r="P51">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="Q51">
         <v>1</v>
@@ -3448,37 +3448,37 @@
     </row>
     <row r="52" spans="1:20">
       <c r="A52">
-        <v>1000</v>
+        <v>1480</v>
       </c>
       <c r="B52">
-        <v>0.03192878009375</v>
+        <v>0.11729412972973</v>
       </c>
       <c r="C52">
-        <v>0.2575</v>
+        <v>0.495</v>
       </c>
       <c r="D52">
-        <v>0.4825</v>
+        <v>0.48</v>
       </c>
       <c r="E52">
-        <v>0.7357136578720045</v>
+        <v>0.9070369568500261</v>
       </c>
       <c r="G52">
-        <v>0.998</v>
+        <v>0.997297297297297</v>
       </c>
       <c r="H52">
-        <v>0.985</v>
+        <v>1</v>
       </c>
       <c r="I52">
         <v>1</v>
       </c>
       <c r="J52">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K52">
         <v>0.5</v>
       </c>
       <c r="L52">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M52">
         <v>1</v>
@@ -3490,13 +3490,13 @@
         <v>1</v>
       </c>
       <c r="P52">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="Q52">
         <v>1</v>
       </c>
       <c r="R52">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="S52">
         <v>1</v>
@@ -3507,37 +3507,37 @@
     </row>
     <row r="53" spans="1:20">
       <c r="A53">
-        <v>1020</v>
+        <v>1500</v>
       </c>
       <c r="B53">
-        <v>0.0319300347120098</v>
+        <v>0.117298368</v>
       </c>
       <c r="C53">
-        <v>0.2575</v>
+        <v>0.495</v>
       </c>
       <c r="D53">
-        <v>0.4825</v>
+        <v>0.48</v>
       </c>
       <c r="E53">
-        <v>0.7357701796669519</v>
+        <v>0.906980435055079</v>
       </c>
       <c r="G53">
-        <v>0.9980392156862745</v>
+        <v>0.997333333333333</v>
       </c>
       <c r="H53">
-        <v>0.995</v>
+        <v>0.99</v>
       </c>
       <c r="I53">
         <v>1</v>
       </c>
       <c r="J53">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K53">
         <v>0.5</v>
       </c>
       <c r="L53">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M53">
         <v>1</v>
@@ -3549,13 +3549,13 @@
         <v>1</v>
       </c>
       <c r="P53">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="Q53">
         <v>1</v>
       </c>
       <c r="R53">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="S53">
         <v>1</v>
@@ -3566,22 +3566,22 @@
     </row>
     <row r="54" spans="1:20">
       <c r="A54">
-        <v>1040</v>
+        <v>1660</v>
       </c>
       <c r="B54">
-        <v>0.03193124107572115</v>
+        <v>0.118550770481928</v>
       </c>
       <c r="C54">
-        <v>0.2575</v>
+        <v>0.495</v>
       </c>
       <c r="D54">
-        <v>0.4825</v>
+        <v>0.485</v>
       </c>
       <c r="E54">
-        <v>0.7357701796669519</v>
+        <v>0.838958470448237</v>
       </c>
       <c r="G54">
-        <v>0.9980769230769231</v>
+        <v>0.9975903614457829</v>
       </c>
       <c r="H54">
         <v>0.995</v>
@@ -3596,10 +3596,10 @@
         <v>0.5</v>
       </c>
       <c r="L54">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M54">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="N54">
         <v>0.5</v>
@@ -3608,13 +3608,13 @@
         <v>1</v>
       </c>
       <c r="P54">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q54">
         <v>1</v>
       </c>
       <c r="R54">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="S54">
         <v>1</v>
@@ -3625,25 +3625,25 @@
     </row>
     <row r="55" spans="1:20">
       <c r="A55">
-        <v>1060</v>
+        <v>1680</v>
       </c>
       <c r="B55">
-        <v>0.03193240191627358</v>
+        <v>0.118554179464286</v>
       </c>
       <c r="C55">
-        <v>0.2575</v>
+        <v>0.495</v>
       </c>
       <c r="D55">
-        <v>0.4825</v>
+        <v>0.485</v>
       </c>
       <c r="E55">
-        <v>0.7357419187694781</v>
+        <v>0.838958470448237</v>
       </c>
       <c r="G55">
-        <v>0.9981132075471698</v>
+        <v>0.997619047619048</v>
       </c>
       <c r="H55">
-        <v>0.99</v>
+        <v>0.995</v>
       </c>
       <c r="I55">
         <v>1</v>
@@ -3655,10 +3655,10 @@
         <v>0.5</v>
       </c>
       <c r="L55">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M55">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="N55">
         <v>0.5</v>
@@ -3667,13 +3667,13 @@
         <v>1</v>
       </c>
       <c r="P55">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q55">
         <v>1</v>
       </c>
       <c r="R55">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="S55">
         <v>1</v>
@@ -3684,25 +3684,25 @@
     </row>
     <row r="56" spans="1:20">
       <c r="A56">
-        <v>1080</v>
+        <v>1700</v>
       </c>
       <c r="B56">
-        <v>0.03193351976273148</v>
+        <v>0.118557508235294</v>
       </c>
       <c r="C56">
-        <v>0.2575</v>
+        <v>0.495</v>
       </c>
       <c r="D56">
-        <v>0.4825</v>
+        <v>0.485</v>
       </c>
       <c r="E56">
-        <v>0.7357984405644256</v>
+        <v>0.838958470448237</v>
       </c>
       <c r="G56">
-        <v>0.9981481481481481</v>
+        <v>0.997647058823529</v>
       </c>
       <c r="H56">
-        <v>1</v>
+        <v>0.995</v>
       </c>
       <c r="I56">
         <v>1</v>
@@ -3714,10 +3714,10 @@
         <v>0.5</v>
       </c>
       <c r="L56">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M56">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="N56">
         <v>0.5</v>
@@ -3726,13 +3726,13 @@
         <v>1</v>
       </c>
       <c r="P56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q56">
         <v>1</v>
       </c>
       <c r="R56">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="S56">
         <v>1</v>
@@ -3743,25 +3743,25 @@
     </row>
     <row r="57" spans="1:20">
       <c r="A57">
-        <v>1100</v>
+        <v>1740</v>
       </c>
       <c r="B57">
-        <v>0.03312636647727273</v>
+        <v>0.120971264367816</v>
       </c>
       <c r="C57">
-        <v>0.2625</v>
+        <v>0.5</v>
       </c>
       <c r="D57">
-        <v>0.4825</v>
+        <v>0.485</v>
       </c>
       <c r="E57">
-        <v>0.7357701796669519</v>
+        <v>0.838930209550763</v>
       </c>
       <c r="G57">
-        <v>0.9963636363636363</v>
+        <v>0.997701149425287</v>
       </c>
       <c r="H57">
-        <v>0.995</v>
+        <v>0.99</v>
       </c>
       <c r="I57">
         <v>1</v>
@@ -3773,10 +3773,10 @@
         <v>0.5</v>
       </c>
       <c r="L57">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M57">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="N57">
         <v>0.5</v>
@@ -3785,13 +3785,13 @@
         <v>1</v>
       </c>
       <c r="P57">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q57">
         <v>1</v>
       </c>
       <c r="R57">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="S57">
         <v>1</v>
@@ -3802,25 +3802,25 @@
     </row>
     <row r="58" spans="1:20">
       <c r="A58">
-        <v>1120</v>
+        <v>1720</v>
       </c>
       <c r="B58">
-        <v>0.033128525390625</v>
+        <v>0.120968023255814</v>
       </c>
       <c r="C58">
-        <v>0.2625</v>
+        <v>0.5</v>
       </c>
       <c r="D58">
-        <v>0.4825</v>
+        <v>0.485</v>
       </c>
       <c r="E58">
-        <v>0.7357701796669519</v>
+        <v>0.838817165960868</v>
       </c>
       <c r="G58">
-        <v>0.9964285714285714</v>
+        <v>0.997674418604651</v>
       </c>
       <c r="H58">
-        <v>0.995</v>
+        <v>0.97</v>
       </c>
       <c r="I58">
         <v>1</v>
@@ -3832,10 +3832,10 @@
         <v>0.5</v>
       </c>
       <c r="L58">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M58">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="N58">
         <v>0.5</v>
@@ -3844,13 +3844,13 @@
         <v>1</v>
       </c>
       <c r="P58">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q58">
         <v>1</v>
       </c>
       <c r="R58">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="S58">
         <v>1</v>
@@ -3861,25 +3861,25 @@
     </row>
     <row r="59" spans="1:20">
       <c r="A59">
-        <v>1140</v>
+        <v>1380</v>
       </c>
       <c r="B59">
-        <v>0.03313060855263158</v>
+        <v>0.120851686956522</v>
       </c>
       <c r="C59">
-        <v>0.2625</v>
+        <v>0.5024999999999999</v>
       </c>
       <c r="D59">
-        <v>0.4825</v>
+        <v>0.48</v>
       </c>
       <c r="E59">
-        <v>0.7357701796669519</v>
+        <v>0.746655146937934</v>
       </c>
       <c r="G59">
-        <v>0.9964912280701754</v>
+        <v>0.997101449275362</v>
       </c>
       <c r="H59">
-        <v>0.995</v>
+        <v>1</v>
       </c>
       <c r="I59">
         <v>1</v>
@@ -3891,7 +3891,7 @@
         <v>0.5</v>
       </c>
       <c r="L59">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M59">
         <v>1</v>
@@ -3920,22 +3920,22 @@
     </row>
     <row r="60" spans="1:20">
       <c r="A60">
-        <v>1160</v>
+        <v>820</v>
       </c>
       <c r="B60">
-        <v>0.03313261988146552</v>
+        <v>0.0329943292682927</v>
       </c>
       <c r="C60">
         <v>0.2625</v>
       </c>
       <c r="D60">
-        <v>0.4825</v>
+        <v>0.48</v>
       </c>
       <c r="E60">
-        <v>0.7357419187694781</v>
+        <v>0.746598625142986</v>
       </c>
       <c r="G60">
-        <v>0.996551724137931</v>
+        <v>0.997560975609756</v>
       </c>
       <c r="H60">
         <v>0.99</v>
@@ -3950,7 +3950,7 @@
         <v>0.5</v>
       </c>
       <c r="L60">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M60">
         <v>1</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="61" spans="1:20">
       <c r="A61">
-        <v>1180</v>
+        <v>840</v>
       </c>
       <c r="B61">
-        <v>0.1202161016949153</v>
+        <v>0.03299625</v>
       </c>
       <c r="C61">
-        <v>0.5</v>
+        <v>0.2625</v>
       </c>
       <c r="D61">
-        <v>0.4825</v>
+        <v>0.48</v>
       </c>
       <c r="E61">
-        <v>0.7357419187694781</v>
+        <v>0.746598625142986</v>
       </c>
       <c r="G61">
-        <v>0.9966101694915255</v>
+        <v>0.997619047619048</v>
       </c>
       <c r="H61">
         <v>0.99</v>
@@ -4009,7 +4009,7 @@
         <v>0.5</v>
       </c>
       <c r="L61">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M61">
         <v>1</v>
@@ -4038,25 +4038,25 @@
     </row>
     <row r="62" spans="1:20">
       <c r="A62">
-        <v>1200</v>
+        <v>1400</v>
       </c>
       <c r="B62">
-        <v>0.00010764</v>
+        <v>0.120856705714286</v>
       </c>
       <c r="C62">
-        <v>0.015</v>
+        <v>0.5024999999999999</v>
       </c>
       <c r="D62">
         <v>0.48</v>
       </c>
       <c r="E62">
-        <v>0.7357419187694781</v>
+        <v>0.746570364245512</v>
       </c>
       <c r="G62">
-        <v>0.9966666666666667</v>
+        <v>0.997142857142857</v>
       </c>
       <c r="H62">
-        <v>0.99</v>
+        <v>0.985</v>
       </c>
       <c r="I62">
         <v>1</v>
@@ -4068,7 +4068,7 @@
         <v>0.5</v>
       </c>
       <c r="L62">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M62">
         <v>1</v>
@@ -4097,25 +4097,25 @@
     </row>
     <row r="63" spans="1:20">
       <c r="A63">
-        <v>1220</v>
+        <v>1080</v>
       </c>
       <c r="B63">
-        <v>0.0001076459016393443</v>
+        <v>0.0319335197627315</v>
       </c>
       <c r="C63">
-        <v>0.015</v>
+        <v>0.2575</v>
       </c>
       <c r="D63">
-        <v>0.48</v>
+        <v>0.4825</v>
       </c>
       <c r="E63">
-        <v>0.7357701796669519</v>
+        <v>0.735798440564426</v>
       </c>
       <c r="G63">
-        <v>0.9967213114754099</v>
+        <v>0.998148148148148</v>
       </c>
       <c r="H63">
-        <v>0.995</v>
+        <v>1</v>
       </c>
       <c r="I63">
         <v>1</v>
@@ -4159,7 +4159,7 @@
         <v>1240</v>
       </c>
       <c r="B64">
-        <v>0.0001465258064516129</v>
+        <v>0.000146525806451613</v>
       </c>
       <c r="C64">
         <v>0.0175</v>
@@ -4168,10 +4168,10 @@
         <v>0.48</v>
       </c>
       <c r="E64">
-        <v>0.7357984405644256</v>
+        <v>0.735798440564426</v>
       </c>
       <c r="G64">
-        <v>0.9967741935483871</v>
+        <v>0.996774193548387</v>
       </c>
       <c r="H64">
         <v>1</v>
@@ -4215,60 +4215,2243 @@
     </row>
     <row r="65" spans="1:20">
       <c r="A65">
-        <v>1260</v>
+        <v>1300</v>
       </c>
       <c r="B65">
-        <v>0.0001465333333333334</v>
+        <v>0.118437452307692</v>
       </c>
       <c r="C65">
-        <v>0.0175</v>
+        <v>0.4975</v>
       </c>
       <c r="D65">
         <v>0.48</v>
       </c>
       <c r="E65">
-        <v>0.7357136578720045</v>
+        <v>0.735798440564426</v>
       </c>
       <c r="G65">
-        <v>0.9968253968253968</v>
+        <v>0.996923076923077</v>
       </c>
       <c r="H65">
+        <v>1</v>
+      </c>
+      <c r="I65">
+        <v>1</v>
+      </c>
+      <c r="J65">
+        <v>1</v>
+      </c>
+      <c r="K65">
+        <v>0.5</v>
+      </c>
+      <c r="L65">
+        <v>0.5</v>
+      </c>
+      <c r="M65">
+        <v>1</v>
+      </c>
+      <c r="N65">
+        <v>0.5</v>
+      </c>
+      <c r="O65">
+        <v>1</v>
+      </c>
+      <c r="P65">
+        <v>1</v>
+      </c>
+      <c r="Q65">
+        <v>1</v>
+      </c>
+      <c r="R65">
+        <v>0.5</v>
+      </c>
+      <c r="S65">
+        <v>1</v>
+      </c>
+      <c r="T65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:20">
+      <c r="A66">
+        <v>1340</v>
+      </c>
+      <c r="B66">
+        <v>0.1208412</v>
+      </c>
+      <c r="C66">
+        <v>0.5024999999999999</v>
+      </c>
+      <c r="D66">
+        <v>0.48</v>
+      </c>
+      <c r="E66">
+        <v>0.735798440564426</v>
+      </c>
+      <c r="G66">
+        <v>0.997014925373134</v>
+      </c>
+      <c r="H66">
+        <v>1</v>
+      </c>
+      <c r="I66">
+        <v>1</v>
+      </c>
+      <c r="J66">
+        <v>1</v>
+      </c>
+      <c r="K66">
+        <v>0.5</v>
+      </c>
+      <c r="L66">
+        <v>0.5</v>
+      </c>
+      <c r="M66">
+        <v>1</v>
+      </c>
+      <c r="N66">
+        <v>0.5</v>
+      </c>
+      <c r="O66">
+        <v>1</v>
+      </c>
+      <c r="P66">
+        <v>1</v>
+      </c>
+      <c r="Q66">
+        <v>1</v>
+      </c>
+      <c r="R66">
+        <v>0.5</v>
+      </c>
+      <c r="S66">
+        <v>1</v>
+      </c>
+      <c r="T66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:20">
+      <c r="A67">
+        <v>1360</v>
+      </c>
+      <c r="B67">
+        <v>0.120846520588235</v>
+      </c>
+      <c r="C67">
+        <v>0.5024999999999999</v>
+      </c>
+      <c r="D67">
+        <v>0.48</v>
+      </c>
+      <c r="E67">
+        <v>0.735798440564426</v>
+      </c>
+      <c r="G67">
+        <v>0.997058823529412</v>
+      </c>
+      <c r="H67">
+        <v>1</v>
+      </c>
+      <c r="I67">
+        <v>1</v>
+      </c>
+      <c r="J67">
+        <v>1</v>
+      </c>
+      <c r="K67">
+        <v>0.5</v>
+      </c>
+      <c r="L67">
+        <v>0.5</v>
+      </c>
+      <c r="M67">
+        <v>1</v>
+      </c>
+      <c r="N67">
+        <v>0.5</v>
+      </c>
+      <c r="O67">
+        <v>1</v>
+      </c>
+      <c r="P67">
+        <v>1</v>
+      </c>
+      <c r="Q67">
+        <v>1</v>
+      </c>
+      <c r="R67">
+        <v>0.5</v>
+      </c>
+      <c r="S67">
+        <v>1</v>
+      </c>
+      <c r="T67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:20">
+      <c r="A68">
+        <v>1020</v>
+      </c>
+      <c r="B68">
+        <v>0.0319300347120098</v>
+      </c>
+      <c r="C68">
+        <v>0.2575</v>
+      </c>
+      <c r="D68">
+        <v>0.4825</v>
+      </c>
+      <c r="E68">
+        <v>0.735770179666952</v>
+      </c>
+      <c r="G68">
+        <v>0.998039215686275</v>
+      </c>
+      <c r="H68">
+        <v>0.995</v>
+      </c>
+      <c r="I68">
+        <v>1</v>
+      </c>
+      <c r="J68">
+        <v>1</v>
+      </c>
+      <c r="K68">
+        <v>0.5</v>
+      </c>
+      <c r="L68">
+        <v>0.5</v>
+      </c>
+      <c r="M68">
+        <v>1</v>
+      </c>
+      <c r="N68">
+        <v>0.5</v>
+      </c>
+      <c r="O68">
+        <v>1</v>
+      </c>
+      <c r="P68">
+        <v>1</v>
+      </c>
+      <c r="Q68">
+        <v>1</v>
+      </c>
+      <c r="R68">
+        <v>0.5</v>
+      </c>
+      <c r="S68">
+        <v>1</v>
+      </c>
+      <c r="T68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:20">
+      <c r="A69">
+        <v>1040</v>
+      </c>
+      <c r="B69">
+        <v>0.0319312410757212</v>
+      </c>
+      <c r="C69">
+        <v>0.2575</v>
+      </c>
+      <c r="D69">
+        <v>0.4825</v>
+      </c>
+      <c r="E69">
+        <v>0.735770179666952</v>
+      </c>
+      <c r="G69">
+        <v>0.998076923076923</v>
+      </c>
+      <c r="H69">
+        <v>0.995</v>
+      </c>
+      <c r="I69">
+        <v>1</v>
+      </c>
+      <c r="J69">
+        <v>1</v>
+      </c>
+      <c r="K69">
+        <v>0.5</v>
+      </c>
+      <c r="L69">
+        <v>0.5</v>
+      </c>
+      <c r="M69">
+        <v>1</v>
+      </c>
+      <c r="N69">
+        <v>0.5</v>
+      </c>
+      <c r="O69">
+        <v>1</v>
+      </c>
+      <c r="P69">
+        <v>1</v>
+      </c>
+      <c r="Q69">
+        <v>1</v>
+      </c>
+      <c r="R69">
+        <v>0.5</v>
+      </c>
+      <c r="S69">
+        <v>1</v>
+      </c>
+      <c r="T69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:20">
+      <c r="A70">
+        <v>1100</v>
+      </c>
+      <c r="B70">
+        <v>0.0331263664772727</v>
+      </c>
+      <c r="C70">
+        <v>0.2625</v>
+      </c>
+      <c r="D70">
+        <v>0.4825</v>
+      </c>
+      <c r="E70">
+        <v>0.735770179666952</v>
+      </c>
+      <c r="G70">
+        <v>0.996363636363636</v>
+      </c>
+      <c r="H70">
+        <v>0.995</v>
+      </c>
+      <c r="I70">
+        <v>1</v>
+      </c>
+      <c r="J70">
+        <v>1</v>
+      </c>
+      <c r="K70">
+        <v>0.5</v>
+      </c>
+      <c r="L70">
+        <v>0.5</v>
+      </c>
+      <c r="M70">
+        <v>1</v>
+      </c>
+      <c r="N70">
+        <v>0.5</v>
+      </c>
+      <c r="O70">
+        <v>1</v>
+      </c>
+      <c r="P70">
+        <v>1</v>
+      </c>
+      <c r="Q70">
+        <v>1</v>
+      </c>
+      <c r="R70">
+        <v>0.5</v>
+      </c>
+      <c r="S70">
+        <v>1</v>
+      </c>
+      <c r="T70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:20">
+      <c r="A71">
+        <v>1120</v>
+      </c>
+      <c r="B71">
+        <v>0.033128525390625</v>
+      </c>
+      <c r="C71">
+        <v>0.2625</v>
+      </c>
+      <c r="D71">
+        <v>0.4825</v>
+      </c>
+      <c r="E71">
+        <v>0.735770179666952</v>
+      </c>
+      <c r="G71">
+        <v>0.996428571428571</v>
+      </c>
+      <c r="H71">
+        <v>0.995</v>
+      </c>
+      <c r="I71">
+        <v>1</v>
+      </c>
+      <c r="J71">
+        <v>1</v>
+      </c>
+      <c r="K71">
+        <v>0.5</v>
+      </c>
+      <c r="L71">
+        <v>0.5</v>
+      </c>
+      <c r="M71">
+        <v>1</v>
+      </c>
+      <c r="N71">
+        <v>0.5</v>
+      </c>
+      <c r="O71">
+        <v>1</v>
+      </c>
+      <c r="P71">
+        <v>1</v>
+      </c>
+      <c r="Q71">
+        <v>1</v>
+      </c>
+      <c r="R71">
+        <v>0.5</v>
+      </c>
+      <c r="S71">
+        <v>1</v>
+      </c>
+      <c r="T71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:20">
+      <c r="A72">
+        <v>1140</v>
+      </c>
+      <c r="B72">
+        <v>0.0331306085526316</v>
+      </c>
+      <c r="C72">
+        <v>0.2625</v>
+      </c>
+      <c r="D72">
+        <v>0.4825</v>
+      </c>
+      <c r="E72">
+        <v>0.735770179666952</v>
+      </c>
+      <c r="G72">
+        <v>0.996491228070175</v>
+      </c>
+      <c r="H72">
+        <v>0.995</v>
+      </c>
+      <c r="I72">
+        <v>1</v>
+      </c>
+      <c r="J72">
+        <v>1</v>
+      </c>
+      <c r="K72">
+        <v>0.5</v>
+      </c>
+      <c r="L72">
+        <v>0.5</v>
+      </c>
+      <c r="M72">
+        <v>1</v>
+      </c>
+      <c r="N72">
+        <v>0.5</v>
+      </c>
+      <c r="O72">
+        <v>1</v>
+      </c>
+      <c r="P72">
+        <v>1</v>
+      </c>
+      <c r="Q72">
+        <v>1</v>
+      </c>
+      <c r="R72">
+        <v>0.5</v>
+      </c>
+      <c r="S72">
+        <v>1</v>
+      </c>
+      <c r="T72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:20">
+      <c r="A73">
+        <v>1220</v>
+      </c>
+      <c r="B73">
+        <v>0.000107645901639344</v>
+      </c>
+      <c r="C73">
+        <v>0.015</v>
+      </c>
+      <c r="D73">
+        <v>0.48</v>
+      </c>
+      <c r="E73">
+        <v>0.735770179666952</v>
+      </c>
+      <c r="G73">
+        <v>0.99672131147541</v>
+      </c>
+      <c r="H73">
+        <v>0.995</v>
+      </c>
+      <c r="I73">
+        <v>1</v>
+      </c>
+      <c r="J73">
+        <v>1</v>
+      </c>
+      <c r="K73">
+        <v>0.5</v>
+      </c>
+      <c r="L73">
+        <v>0.5</v>
+      </c>
+      <c r="M73">
+        <v>1</v>
+      </c>
+      <c r="N73">
+        <v>0.5</v>
+      </c>
+      <c r="O73">
+        <v>1</v>
+      </c>
+      <c r="P73">
+        <v>1</v>
+      </c>
+      <c r="Q73">
+        <v>1</v>
+      </c>
+      <c r="R73">
+        <v>0.5</v>
+      </c>
+      <c r="S73">
+        <v>1</v>
+      </c>
+      <c r="T73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:20">
+      <c r="A74">
+        <v>1280</v>
+      </c>
+      <c r="B74">
+        <v>0.118431740625</v>
+      </c>
+      <c r="C74">
+        <v>0.4975</v>
+      </c>
+      <c r="D74">
+        <v>0.48</v>
+      </c>
+      <c r="E74">
+        <v>0.735770179666952</v>
+      </c>
+      <c r="G74">
+        <v>0.996875</v>
+      </c>
+      <c r="H74">
+        <v>0.995</v>
+      </c>
+      <c r="I74">
+        <v>1</v>
+      </c>
+      <c r="J74">
+        <v>1</v>
+      </c>
+      <c r="K74">
+        <v>0.5</v>
+      </c>
+      <c r="L74">
+        <v>0.5</v>
+      </c>
+      <c r="M74">
+        <v>1</v>
+      </c>
+      <c r="N74">
+        <v>0.5</v>
+      </c>
+      <c r="O74">
+        <v>1</v>
+      </c>
+      <c r="P74">
+        <v>1</v>
+      </c>
+      <c r="Q74">
+        <v>1</v>
+      </c>
+      <c r="R74">
+        <v>0.5</v>
+      </c>
+      <c r="S74">
+        <v>1</v>
+      </c>
+      <c r="T74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:20">
+      <c r="A75">
+        <v>1320</v>
+      </c>
+      <c r="B75">
+        <v>0.118442990909091</v>
+      </c>
+      <c r="C75">
+        <v>0.4975</v>
+      </c>
+      <c r="D75">
+        <v>0.48</v>
+      </c>
+      <c r="E75">
+        <v>0.735770179666952</v>
+      </c>
+      <c r="G75">
+        <v>0.996969696969697</v>
+      </c>
+      <c r="H75">
+        <v>0.995</v>
+      </c>
+      <c r="I75">
+        <v>1</v>
+      </c>
+      <c r="J75">
+        <v>1</v>
+      </c>
+      <c r="K75">
+        <v>0.5</v>
+      </c>
+      <c r="L75">
+        <v>0.5</v>
+      </c>
+      <c r="M75">
+        <v>1</v>
+      </c>
+      <c r="N75">
+        <v>0.5</v>
+      </c>
+      <c r="O75">
+        <v>1</v>
+      </c>
+      <c r="P75">
+        <v>1</v>
+      </c>
+      <c r="Q75">
+        <v>1</v>
+      </c>
+      <c r="R75">
+        <v>0.5</v>
+      </c>
+      <c r="S75">
+        <v>1</v>
+      </c>
+      <c r="T75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:20">
+      <c r="A76">
+        <v>560</v>
+      </c>
+      <c r="B76">
+        <v>0.0317133321428571</v>
+      </c>
+      <c r="C76">
+        <v>0.2575</v>
+      </c>
+      <c r="D76">
+        <v>0.48</v>
+      </c>
+      <c r="E76">
+        <v>0.735741918769478</v>
+      </c>
+      <c r="G76">
+        <v>0.996428571428571</v>
+      </c>
+      <c r="H76">
+        <v>0.99</v>
+      </c>
+      <c r="I76">
+        <v>1</v>
+      </c>
+      <c r="J76">
+        <v>1</v>
+      </c>
+      <c r="K76">
+        <v>0.5</v>
+      </c>
+      <c r="L76">
+        <v>0.5</v>
+      </c>
+      <c r="M76">
+        <v>1</v>
+      </c>
+      <c r="N76">
+        <v>0.5</v>
+      </c>
+      <c r="O76">
+        <v>1</v>
+      </c>
+      <c r="P76">
+        <v>1</v>
+      </c>
+      <c r="Q76">
+        <v>1</v>
+      </c>
+      <c r="R76">
+        <v>0.5</v>
+      </c>
+      <c r="S76">
+        <v>1</v>
+      </c>
+      <c r="T76">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:20">
+      <c r="A77">
+        <v>580</v>
+      </c>
+      <c r="B77">
+        <v>0.0317172517241379</v>
+      </c>
+      <c r="C77">
+        <v>0.2575</v>
+      </c>
+      <c r="D77">
+        <v>0.48</v>
+      </c>
+      <c r="E77">
+        <v>0.735741918769478</v>
+      </c>
+      <c r="G77">
+        <v>0.996551724137931</v>
+      </c>
+      <c r="H77">
+        <v>0.99</v>
+      </c>
+      <c r="I77">
+        <v>1</v>
+      </c>
+      <c r="J77">
+        <v>1</v>
+      </c>
+      <c r="K77">
+        <v>0.5</v>
+      </c>
+      <c r="L77">
+        <v>0.5</v>
+      </c>
+      <c r="M77">
+        <v>1</v>
+      </c>
+      <c r="N77">
+        <v>0.5</v>
+      </c>
+      <c r="O77">
+        <v>1</v>
+      </c>
+      <c r="P77">
+        <v>1</v>
+      </c>
+      <c r="Q77">
+        <v>1</v>
+      </c>
+      <c r="R77">
+        <v>0.5</v>
+      </c>
+      <c r="S77">
+        <v>1</v>
+      </c>
+      <c r="T77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:20">
+      <c r="A78">
+        <v>860</v>
+      </c>
+      <c r="B78">
+        <v>0.0329980813953488</v>
+      </c>
+      <c r="C78">
+        <v>0.2625</v>
+      </c>
+      <c r="D78">
+        <v>0.48</v>
+      </c>
+      <c r="E78">
+        <v>0.735741918769478</v>
+      </c>
+      <c r="G78">
+        <v>0.997674418604651</v>
+      </c>
+      <c r="H78">
+        <v>0.99</v>
+      </c>
+      <c r="I78">
+        <v>1</v>
+      </c>
+      <c r="J78">
+        <v>1</v>
+      </c>
+      <c r="K78">
+        <v>0.5</v>
+      </c>
+      <c r="L78">
+        <v>0.5</v>
+      </c>
+      <c r="M78">
+        <v>1</v>
+      </c>
+      <c r="N78">
+        <v>0.5</v>
+      </c>
+      <c r="O78">
+        <v>1</v>
+      </c>
+      <c r="P78">
+        <v>1</v>
+      </c>
+      <c r="Q78">
+        <v>1</v>
+      </c>
+      <c r="R78">
+        <v>0.5</v>
+      </c>
+      <c r="S78">
+        <v>1</v>
+      </c>
+      <c r="T78">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:20">
+      <c r="A79">
+        <v>1060</v>
+      </c>
+      <c r="B79">
+        <v>0.0319324019162736</v>
+      </c>
+      <c r="C79">
+        <v>0.2575</v>
+      </c>
+      <c r="D79">
+        <v>0.4825</v>
+      </c>
+      <c r="E79">
+        <v>0.735741918769478</v>
+      </c>
+      <c r="G79">
+        <v>0.99811320754717</v>
+      </c>
+      <c r="H79">
+        <v>0.99</v>
+      </c>
+      <c r="I79">
+        <v>1</v>
+      </c>
+      <c r="J79">
+        <v>1</v>
+      </c>
+      <c r="K79">
+        <v>0.5</v>
+      </c>
+      <c r="L79">
+        <v>0.5</v>
+      </c>
+      <c r="M79">
+        <v>1</v>
+      </c>
+      <c r="N79">
+        <v>0.5</v>
+      </c>
+      <c r="O79">
+        <v>1</v>
+      </c>
+      <c r="P79">
+        <v>1</v>
+      </c>
+      <c r="Q79">
+        <v>1</v>
+      </c>
+      <c r="R79">
+        <v>0.5</v>
+      </c>
+      <c r="S79">
+        <v>1</v>
+      </c>
+      <c r="T79">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:20">
+      <c r="A80">
+        <v>1160</v>
+      </c>
+      <c r="B80">
+        <v>0.0331326198814655</v>
+      </c>
+      <c r="C80">
+        <v>0.2625</v>
+      </c>
+      <c r="D80">
+        <v>0.4825</v>
+      </c>
+      <c r="E80">
+        <v>0.735741918769478</v>
+      </c>
+      <c r="G80">
+        <v>0.996551724137931</v>
+      </c>
+      <c r="H80">
+        <v>0.99</v>
+      </c>
+      <c r="I80">
+        <v>1</v>
+      </c>
+      <c r="J80">
+        <v>1</v>
+      </c>
+      <c r="K80">
+        <v>0.5</v>
+      </c>
+      <c r="L80">
+        <v>0.5</v>
+      </c>
+      <c r="M80">
+        <v>1</v>
+      </c>
+      <c r="N80">
+        <v>0.5</v>
+      </c>
+      <c r="O80">
+        <v>1</v>
+      </c>
+      <c r="P80">
+        <v>1</v>
+      </c>
+      <c r="Q80">
+        <v>1</v>
+      </c>
+      <c r="R80">
+        <v>0.5</v>
+      </c>
+      <c r="S80">
+        <v>1</v>
+      </c>
+      <c r="T80">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:20">
+      <c r="A81">
+        <v>1180</v>
+      </c>
+      <c r="B81">
+        <v>0.120216101694915</v>
+      </c>
+      <c r="C81">
+        <v>0.5</v>
+      </c>
+      <c r="D81">
+        <v>0.4825</v>
+      </c>
+      <c r="E81">
+        <v>0.735741918769478</v>
+      </c>
+      <c r="G81">
+        <v>0.996610169491526</v>
+      </c>
+      <c r="H81">
+        <v>0.99</v>
+      </c>
+      <c r="I81">
+        <v>1</v>
+      </c>
+      <c r="J81">
+        <v>1</v>
+      </c>
+      <c r="K81">
+        <v>0.5</v>
+      </c>
+      <c r="L81">
+        <v>0.5</v>
+      </c>
+      <c r="M81">
+        <v>1</v>
+      </c>
+      <c r="N81">
+        <v>0.5</v>
+      </c>
+      <c r="O81">
+        <v>1</v>
+      </c>
+      <c r="P81">
+        <v>1</v>
+      </c>
+      <c r="Q81">
+        <v>1</v>
+      </c>
+      <c r="R81">
+        <v>0.5</v>
+      </c>
+      <c r="S81">
+        <v>1</v>
+      </c>
+      <c r="T81">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:20">
+      <c r="A82">
+        <v>1200</v>
+      </c>
+      <c r="B82">
+        <v>0.00010764</v>
+      </c>
+      <c r="C82">
+        <v>0.015</v>
+      </c>
+      <c r="D82">
+        <v>0.48</v>
+      </c>
+      <c r="E82">
+        <v>0.735741918769478</v>
+      </c>
+      <c r="G82">
+        <v>0.996666666666667</v>
+      </c>
+      <c r="H82">
+        <v>0.99</v>
+      </c>
+      <c r="I82">
+        <v>1</v>
+      </c>
+      <c r="J82">
+        <v>1</v>
+      </c>
+      <c r="K82">
+        <v>0.5</v>
+      </c>
+      <c r="L82">
+        <v>0.5</v>
+      </c>
+      <c r="M82">
+        <v>1</v>
+      </c>
+      <c r="N82">
+        <v>0.5</v>
+      </c>
+      <c r="O82">
+        <v>1</v>
+      </c>
+      <c r="P82">
+        <v>1</v>
+      </c>
+      <c r="Q82">
+        <v>1</v>
+      </c>
+      <c r="R82">
+        <v>0.5</v>
+      </c>
+      <c r="S82">
+        <v>1</v>
+      </c>
+      <c r="T82">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:20">
+      <c r="A83">
+        <v>880</v>
+      </c>
+      <c r="B83">
+        <v>0.0329998295454545</v>
+      </c>
+      <c r="C83">
+        <v>0.2625</v>
+      </c>
+      <c r="D83">
+        <v>0.48</v>
+      </c>
+      <c r="E83">
+        <v>0.735713657872005</v>
+      </c>
+      <c r="G83">
+        <v>0.997727272727273</v>
+      </c>
+      <c r="H83">
         <v>0.985</v>
       </c>
-      <c r="I65">
-        <v>1</v>
-      </c>
-      <c r="J65">
-        <v>1</v>
-      </c>
-      <c r="K65">
-        <v>0.5</v>
-      </c>
-      <c r="L65">
-        <v>0.5</v>
-      </c>
-      <c r="M65">
-        <v>1</v>
-      </c>
-      <c r="N65">
-        <v>0.5</v>
-      </c>
-      <c r="O65">
-        <v>1</v>
-      </c>
-      <c r="P65">
-        <v>1</v>
-      </c>
-      <c r="Q65">
-        <v>1</v>
-      </c>
-      <c r="R65">
-        <v>0.5</v>
-      </c>
-      <c r="S65">
-        <v>1</v>
-      </c>
-      <c r="T65">
+      <c r="I83">
+        <v>1</v>
+      </c>
+      <c r="J83">
+        <v>1</v>
+      </c>
+      <c r="K83">
+        <v>0.5</v>
+      </c>
+      <c r="L83">
+        <v>0.5</v>
+      </c>
+      <c r="M83">
+        <v>1</v>
+      </c>
+      <c r="N83">
+        <v>0.5</v>
+      </c>
+      <c r="O83">
+        <v>1</v>
+      </c>
+      <c r="P83">
+        <v>1</v>
+      </c>
+      <c r="Q83">
+        <v>1</v>
+      </c>
+      <c r="R83">
+        <v>0.5</v>
+      </c>
+      <c r="S83">
+        <v>1</v>
+      </c>
+      <c r="T83">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:20">
+      <c r="A84">
+        <v>1000</v>
+      </c>
+      <c r="B84">
+        <v>0.03192878009375</v>
+      </c>
+      <c r="C84">
+        <v>0.2575</v>
+      </c>
+      <c r="D84">
+        <v>0.4825</v>
+      </c>
+      <c r="E84">
+        <v>0.735713657872005</v>
+      </c>
+      <c r="G84">
+        <v>0.998</v>
+      </c>
+      <c r="H84">
+        <v>0.985</v>
+      </c>
+      <c r="I84">
+        <v>1</v>
+      </c>
+      <c r="J84">
+        <v>1</v>
+      </c>
+      <c r="K84">
+        <v>0.5</v>
+      </c>
+      <c r="L84">
+        <v>0.5</v>
+      </c>
+      <c r="M84">
+        <v>1</v>
+      </c>
+      <c r="N84">
+        <v>0.5</v>
+      </c>
+      <c r="O84">
+        <v>1</v>
+      </c>
+      <c r="P84">
+        <v>1</v>
+      </c>
+      <c r="Q84">
+        <v>1</v>
+      </c>
+      <c r="R84">
+        <v>0.5</v>
+      </c>
+      <c r="S84">
+        <v>1</v>
+      </c>
+      <c r="T84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:20">
+      <c r="A85">
+        <v>1260</v>
+      </c>
+      <c r="B85">
+        <v>0.000146533333333333</v>
+      </c>
+      <c r="C85">
+        <v>0.0175</v>
+      </c>
+      <c r="D85">
+        <v>0.48</v>
+      </c>
+      <c r="E85">
+        <v>0.735713657872005</v>
+      </c>
+      <c r="G85">
+        <v>0.9968253968253969</v>
+      </c>
+      <c r="H85">
+        <v>0.985</v>
+      </c>
+      <c r="I85">
+        <v>1</v>
+      </c>
+      <c r="J85">
+        <v>1</v>
+      </c>
+      <c r="K85">
+        <v>0.5</v>
+      </c>
+      <c r="L85">
+        <v>0.5</v>
+      </c>
+      <c r="M85">
+        <v>1</v>
+      </c>
+      <c r="N85">
+        <v>0.5</v>
+      </c>
+      <c r="O85">
+        <v>1</v>
+      </c>
+      <c r="P85">
+        <v>1</v>
+      </c>
+      <c r="Q85">
+        <v>1</v>
+      </c>
+      <c r="R85">
+        <v>0.5</v>
+      </c>
+      <c r="S85">
+        <v>1</v>
+      </c>
+      <c r="T85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:20">
+      <c r="A86">
+        <v>600</v>
+      </c>
+      <c r="B86">
+        <v>0.03172091</v>
+      </c>
+      <c r="C86">
+        <v>0.2575</v>
+      </c>
+      <c r="D86">
+        <v>0.48</v>
+      </c>
+      <c r="E86">
+        <v>0.730202782864627</v>
+      </c>
+      <c r="G86">
+        <v>0.996666666666667</v>
+      </c>
+      <c r="H86">
+        <v>0.99</v>
+      </c>
+      <c r="I86">
+        <v>1</v>
+      </c>
+      <c r="J86">
+        <v>0.5</v>
+      </c>
+      <c r="K86">
+        <v>0.5</v>
+      </c>
+      <c r="L86">
+        <v>0.5</v>
+      </c>
+      <c r="M86">
+        <v>1</v>
+      </c>
+      <c r="N86">
+        <v>0.5</v>
+      </c>
+      <c r="O86">
+        <v>1</v>
+      </c>
+      <c r="P86">
+        <v>1</v>
+      </c>
+      <c r="Q86">
+        <v>1</v>
+      </c>
+      <c r="R86">
+        <v>0.5</v>
+      </c>
+      <c r="S86">
+        <v>1</v>
+      </c>
+      <c r="T86">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:20">
+      <c r="A87">
+        <v>620</v>
+      </c>
+      <c r="B87">
+        <v>0.0317243322580645</v>
+      </c>
+      <c r="C87">
+        <v>0.2575</v>
+      </c>
+      <c r="D87">
+        <v>0.48</v>
+      </c>
+      <c r="E87">
+        <v>0.730174521967153</v>
+      </c>
+      <c r="G87">
+        <v>0.996774193548387</v>
+      </c>
+      <c r="H87">
+        <v>0.985</v>
+      </c>
+      <c r="I87">
+        <v>1</v>
+      </c>
+      <c r="J87">
+        <v>0.5</v>
+      </c>
+      <c r="K87">
+        <v>0.5</v>
+      </c>
+      <c r="L87">
+        <v>0.5</v>
+      </c>
+      <c r="M87">
+        <v>1</v>
+      </c>
+      <c r="N87">
+        <v>0.5</v>
+      </c>
+      <c r="O87">
+        <v>1</v>
+      </c>
+      <c r="P87">
+        <v>1</v>
+      </c>
+      <c r="Q87">
+        <v>1</v>
+      </c>
+      <c r="R87">
+        <v>0.5</v>
+      </c>
+      <c r="S87">
+        <v>1</v>
+      </c>
+      <c r="T87">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:20">
+      <c r="A88">
+        <v>40</v>
+      </c>
+      <c r="B88">
+        <v>0.12125</v>
+      </c>
+      <c r="C88">
+        <v>0.5</v>
+      </c>
+      <c r="D88">
+        <v>0.485</v>
+      </c>
+      <c r="E88">
+        <v>0.690779988455135</v>
+      </c>
+      <c r="G88">
+        <v>1</v>
+      </c>
+      <c r="H88">
+        <v>0.995</v>
+      </c>
+      <c r="I88">
+        <v>1</v>
+      </c>
+      <c r="J88">
+        <v>1</v>
+      </c>
+      <c r="K88">
+        <v>0.5</v>
+      </c>
+      <c r="L88">
+        <v>0.5</v>
+      </c>
+      <c r="M88">
+        <v>0.5</v>
+      </c>
+      <c r="N88">
+        <v>0.5</v>
+      </c>
+      <c r="O88">
+        <v>0.5</v>
+      </c>
+      <c r="P88">
+        <v>1</v>
+      </c>
+      <c r="Q88">
+        <v>1</v>
+      </c>
+      <c r="R88">
+        <v>0.5</v>
+      </c>
+      <c r="S88">
+        <v>1</v>
+      </c>
+      <c r="T88">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:20">
+      <c r="A89">
+        <v>60</v>
+      </c>
+      <c r="B89">
+        <v>0.12125</v>
+      </c>
+      <c r="C89">
+        <v>0.5</v>
+      </c>
+      <c r="D89">
+        <v>0.485</v>
+      </c>
+      <c r="E89">
+        <v>0.690779988455135</v>
+      </c>
+      <c r="G89">
+        <v>1</v>
+      </c>
+      <c r="H89">
+        <v>0.995</v>
+      </c>
+      <c r="I89">
+        <v>1</v>
+      </c>
+      <c r="J89">
+        <v>1</v>
+      </c>
+      <c r="K89">
+        <v>0.5</v>
+      </c>
+      <c r="L89">
+        <v>0.5</v>
+      </c>
+      <c r="M89">
+        <v>0.5</v>
+      </c>
+      <c r="N89">
+        <v>0.5</v>
+      </c>
+      <c r="O89">
+        <v>0.5</v>
+      </c>
+      <c r="P89">
+        <v>1</v>
+      </c>
+      <c r="Q89">
+        <v>1</v>
+      </c>
+      <c r="R89">
+        <v>0.5</v>
+      </c>
+      <c r="S89">
+        <v>1</v>
+      </c>
+      <c r="T89">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:20">
+      <c r="A90">
+        <v>1760</v>
+      </c>
+      <c r="B90">
+        <v>0.119727272727273</v>
+      </c>
+      <c r="C90">
+        <v>0.5</v>
+      </c>
+      <c r="D90">
+        <v>0.48</v>
+      </c>
+      <c r="E90">
+        <v>0.614619291247564</v>
+      </c>
+      <c r="G90">
+        <v>0.997727272727273</v>
+      </c>
+      <c r="H90">
+        <v>0.99</v>
+      </c>
+      <c r="I90">
+        <v>1</v>
+      </c>
+      <c r="J90">
+        <v>1</v>
+      </c>
+      <c r="K90">
+        <v>0.5</v>
+      </c>
+      <c r="L90">
+        <v>1</v>
+      </c>
+      <c r="M90">
+        <v>0.5</v>
+      </c>
+      <c r="N90">
+        <v>0.5</v>
+      </c>
+      <c r="O90">
+        <v>1</v>
+      </c>
+      <c r="P90">
+        <v>0</v>
+      </c>
+      <c r="Q90">
+        <v>1</v>
+      </c>
+      <c r="R90">
+        <v>0.5</v>
+      </c>
+      <c r="S90">
+        <v>1</v>
+      </c>
+      <c r="T90">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:20">
+      <c r="A91">
+        <v>1780</v>
+      </c>
+      <c r="B91">
+        <v>0.1197303370786517</v>
+      </c>
+      <c r="C91">
+        <v>0.5</v>
+      </c>
+      <c r="D91">
+        <v>0.48</v>
+      </c>
+      <c r="E91">
+        <v>0.6146192912475639</v>
+      </c>
+      <c r="G91">
+        <v>0.9977528089887641</v>
+      </c>
+      <c r="H91">
+        <v>0.99</v>
+      </c>
+      <c r="I91">
+        <v>1</v>
+      </c>
+      <c r="J91">
+        <v>1</v>
+      </c>
+      <c r="K91">
+        <v>0.5</v>
+      </c>
+      <c r="L91">
+        <v>1</v>
+      </c>
+      <c r="M91">
+        <v>0.5</v>
+      </c>
+      <c r="N91">
+        <v>0.5</v>
+      </c>
+      <c r="O91">
+        <v>1</v>
+      </c>
+      <c r="P91">
+        <v>0</v>
+      </c>
+      <c r="Q91">
+        <v>1</v>
+      </c>
+      <c r="R91">
+        <v>0.5</v>
+      </c>
+      <c r="S91">
+        <v>1</v>
+      </c>
+      <c r="T91">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:20">
+      <c r="A92">
+        <v>1800</v>
+      </c>
+      <c r="B92">
+        <v>0.1197333333333333</v>
+      </c>
+      <c r="C92">
+        <v>0.5</v>
+      </c>
+      <c r="D92">
+        <v>0.48</v>
+      </c>
+      <c r="E92">
+        <v>0.6146758130425113</v>
+      </c>
+      <c r="G92">
+        <v>0.9977777777777778</v>
+      </c>
+      <c r="H92">
+        <v>1</v>
+      </c>
+      <c r="I92">
+        <v>1</v>
+      </c>
+      <c r="J92">
+        <v>1</v>
+      </c>
+      <c r="K92">
+        <v>0.5</v>
+      </c>
+      <c r="L92">
+        <v>1</v>
+      </c>
+      <c r="M92">
+        <v>0.5</v>
+      </c>
+      <c r="N92">
+        <v>0.5</v>
+      </c>
+      <c r="O92">
+        <v>1</v>
+      </c>
+      <c r="P92">
+        <v>0</v>
+      </c>
+      <c r="Q92">
+        <v>1</v>
+      </c>
+      <c r="R92">
+        <v>0.5</v>
+      </c>
+      <c r="S92">
+        <v>1</v>
+      </c>
+      <c r="T92">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:20">
+      <c r="A93">
+        <v>1820</v>
+      </c>
+      <c r="B93">
+        <v>0.1197362637362637</v>
+      </c>
+      <c r="C93">
+        <v>0.5</v>
+      </c>
+      <c r="D93">
+        <v>0.48</v>
+      </c>
+      <c r="E93">
+        <v>0.6146192912475639</v>
+      </c>
+      <c r="G93">
+        <v>0.9978021978021978</v>
+      </c>
+      <c r="H93">
+        <v>0.99</v>
+      </c>
+      <c r="I93">
+        <v>1</v>
+      </c>
+      <c r="J93">
+        <v>1</v>
+      </c>
+      <c r="K93">
+        <v>0.5</v>
+      </c>
+      <c r="L93">
+        <v>1</v>
+      </c>
+      <c r="M93">
+        <v>0.5</v>
+      </c>
+      <c r="N93">
+        <v>0.5</v>
+      </c>
+      <c r="O93">
+        <v>1</v>
+      </c>
+      <c r="P93">
+        <v>0</v>
+      </c>
+      <c r="Q93">
+        <v>1</v>
+      </c>
+      <c r="R93">
+        <v>0.5</v>
+      </c>
+      <c r="S93">
+        <v>1</v>
+      </c>
+      <c r="T93">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:20">
+      <c r="A94">
+        <v>1840</v>
+      </c>
+      <c r="B94">
+        <v>0.1234182399456522</v>
+      </c>
+      <c r="C94">
+        <v>0.505</v>
+      </c>
+      <c r="D94">
+        <v>0.485</v>
+      </c>
+      <c r="E94">
+        <v>0.6730092637338194</v>
+      </c>
+      <c r="G94">
+        <v>0.9978260869565218</v>
+      </c>
+      <c r="H94">
+        <v>0.99</v>
+      </c>
+      <c r="I94">
+        <v>1</v>
+      </c>
+      <c r="J94">
+        <v>1</v>
+      </c>
+      <c r="K94">
+        <v>0.5</v>
+      </c>
+      <c r="L94">
+        <v>1</v>
+      </c>
+      <c r="M94">
+        <v>0.5</v>
+      </c>
+      <c r="N94">
+        <v>0.5</v>
+      </c>
+      <c r="O94">
+        <v>1</v>
+      </c>
+      <c r="P94">
+        <v>0.5</v>
+      </c>
+      <c r="Q94">
+        <v>1</v>
+      </c>
+      <c r="R94">
+        <v>0.5</v>
+      </c>
+      <c r="S94">
+        <v>1</v>
+      </c>
+      <c r="T94">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:20">
+      <c r="A95">
+        <v>1860</v>
+      </c>
+      <c r="B95">
+        <v>0.1234211311827957</v>
+      </c>
+      <c r="C95">
+        <v>0.505</v>
+      </c>
+      <c r="D95">
+        <v>0.485</v>
+      </c>
+      <c r="E95">
+        <v>0.6730092637338194</v>
+      </c>
+      <c r="G95">
+        <v>0.9978494623655914</v>
+      </c>
+      <c r="H95">
+        <v>0.99</v>
+      </c>
+      <c r="I95">
+        <v>1</v>
+      </c>
+      <c r="J95">
+        <v>1</v>
+      </c>
+      <c r="K95">
+        <v>0.5</v>
+      </c>
+      <c r="L95">
+        <v>1</v>
+      </c>
+      <c r="M95">
+        <v>0.5</v>
+      </c>
+      <c r="N95">
+        <v>0.5</v>
+      </c>
+      <c r="O95">
+        <v>1</v>
+      </c>
+      <c r="P95">
+        <v>0.5</v>
+      </c>
+      <c r="Q95">
+        <v>1</v>
+      </c>
+      <c r="R95">
+        <v>0.5</v>
+      </c>
+      <c r="S95">
+        <v>1</v>
+      </c>
+      <c r="T95">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:20">
+      <c r="A96">
+        <v>1880</v>
+      </c>
+      <c r="B96">
+        <v>0.1209920212765958</v>
+      </c>
+      <c r="C96">
+        <v>0.5</v>
+      </c>
+      <c r="D96">
+        <v>0.485</v>
+      </c>
+      <c r="E96">
+        <v>0.6730375246312932</v>
+      </c>
+      <c r="G96">
+        <v>0.997872340425532</v>
+      </c>
+      <c r="H96">
+        <v>0.995</v>
+      </c>
+      <c r="I96">
+        <v>1</v>
+      </c>
+      <c r="J96">
+        <v>1</v>
+      </c>
+      <c r="K96">
+        <v>0.5</v>
+      </c>
+      <c r="L96">
+        <v>1</v>
+      </c>
+      <c r="M96">
+        <v>0.5</v>
+      </c>
+      <c r="N96">
+        <v>0.5</v>
+      </c>
+      <c r="O96">
+        <v>1</v>
+      </c>
+      <c r="P96">
+        <v>0.5</v>
+      </c>
+      <c r="Q96">
+        <v>1</v>
+      </c>
+      <c r="R96">
+        <v>0.5</v>
+      </c>
+      <c r="S96">
+        <v>1</v>
+      </c>
+      <c r="T96">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:20">
+      <c r="A97">
+        <v>1900</v>
+      </c>
+      <c r="B97">
+        <v>0.1209947368421053</v>
+      </c>
+      <c r="C97">
+        <v>0.5</v>
+      </c>
+      <c r="D97">
+        <v>0.485</v>
+      </c>
+      <c r="E97">
+        <v>0.672952741938872</v>
+      </c>
+      <c r="G97">
+        <v>0.9978947368421053</v>
+      </c>
+      <c r="H97">
+        <v>0.98</v>
+      </c>
+      <c r="I97">
+        <v>1</v>
+      </c>
+      <c r="J97">
+        <v>1</v>
+      </c>
+      <c r="K97">
+        <v>0.5</v>
+      </c>
+      <c r="L97">
+        <v>1</v>
+      </c>
+      <c r="M97">
+        <v>0.5</v>
+      </c>
+      <c r="N97">
+        <v>0.5</v>
+      </c>
+      <c r="O97">
+        <v>1</v>
+      </c>
+      <c r="P97">
+        <v>0.5</v>
+      </c>
+      <c r="Q97">
+        <v>1</v>
+      </c>
+      <c r="R97">
+        <v>0.5</v>
+      </c>
+      <c r="S97">
+        <v>1</v>
+      </c>
+      <c r="T97">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:20">
+      <c r="A98">
+        <v>1920</v>
+      </c>
+      <c r="B98">
+        <v>0.1234294434895833</v>
+      </c>
+      <c r="C98">
+        <v>0.505</v>
+      </c>
+      <c r="D98">
+        <v>0.485</v>
+      </c>
+      <c r="E98">
+        <v>0.6730657855287668</v>
+      </c>
+      <c r="G98">
+        <v>0.9979166666666667</v>
+      </c>
+      <c r="H98">
+        <v>1</v>
+      </c>
+      <c r="I98">
+        <v>1</v>
+      </c>
+      <c r="J98">
+        <v>1</v>
+      </c>
+      <c r="K98">
+        <v>0.5</v>
+      </c>
+      <c r="L98">
+        <v>1</v>
+      </c>
+      <c r="M98">
+        <v>0.5</v>
+      </c>
+      <c r="N98">
+        <v>0.5</v>
+      </c>
+      <c r="O98">
+        <v>1</v>
+      </c>
+      <c r="P98">
+        <v>0.5</v>
+      </c>
+      <c r="Q98">
+        <v>1</v>
+      </c>
+      <c r="R98">
+        <v>0.5</v>
+      </c>
+      <c r="S98">
+        <v>1</v>
+      </c>
+      <c r="T98">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:20">
+      <c r="A99">
+        <v>1940</v>
+      </c>
+      <c r="B99">
+        <v>0.1234321</v>
+      </c>
+      <c r="C99">
+        <v>0.505</v>
+      </c>
+      <c r="D99">
+        <v>0.485</v>
+      </c>
+      <c r="E99">
+        <v>0.6730092637338194</v>
+      </c>
+      <c r="G99">
+        <v>0.9979381443298969</v>
+      </c>
+      <c r="H99">
+        <v>0.99</v>
+      </c>
+      <c r="I99">
+        <v>1</v>
+      </c>
+      <c r="J99">
+        <v>1</v>
+      </c>
+      <c r="K99">
+        <v>0.5</v>
+      </c>
+      <c r="L99">
+        <v>1</v>
+      </c>
+      <c r="M99">
+        <v>0.5</v>
+      </c>
+      <c r="N99">
+        <v>0.5</v>
+      </c>
+      <c r="O99">
+        <v>1</v>
+      </c>
+      <c r="P99">
+        <v>0.5</v>
+      </c>
+      <c r="Q99">
+        <v>1</v>
+      </c>
+      <c r="R99">
+        <v>0.5</v>
+      </c>
+      <c r="S99">
+        <v>1</v>
+      </c>
+      <c r="T99">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:20">
+      <c r="A100">
+        <v>1960</v>
+      </c>
+      <c r="B100">
+        <v>0.1234347022959184</v>
+      </c>
+      <c r="C100">
+        <v>0.505</v>
+      </c>
+      <c r="D100">
+        <v>0.485</v>
+      </c>
+      <c r="E100">
+        <v>0.672952741938872</v>
+      </c>
+      <c r="G100">
+        <v>0.9979591836734694</v>
+      </c>
+      <c r="H100">
+        <v>0.98</v>
+      </c>
+      <c r="I100">
+        <v>1</v>
+      </c>
+      <c r="J100">
+        <v>1</v>
+      </c>
+      <c r="K100">
+        <v>0.5</v>
+      </c>
+      <c r="L100">
+        <v>1</v>
+      </c>
+      <c r="M100">
+        <v>0.5</v>
+      </c>
+      <c r="N100">
+        <v>0.5</v>
+      </c>
+      <c r="O100">
+        <v>1</v>
+      </c>
+      <c r="P100">
+        <v>0.5</v>
+      </c>
+      <c r="Q100">
+        <v>1</v>
+      </c>
+      <c r="R100">
+        <v>0.5</v>
+      </c>
+      <c r="S100">
+        <v>1</v>
+      </c>
+      <c r="T100">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:20">
+      <c r="A101">
+        <v>1980</v>
+      </c>
+      <c r="B101">
+        <v>0.1210050505050505</v>
+      </c>
+      <c r="C101">
+        <v>0.5</v>
+      </c>
+      <c r="D101">
+        <v>0.485</v>
+      </c>
+      <c r="E101">
+        <v>0.6730092637338194</v>
+      </c>
+      <c r="G101">
+        <v>0.997979797979798</v>
+      </c>
+      <c r="H101">
+        <v>0.99</v>
+      </c>
+      <c r="I101">
+        <v>1</v>
+      </c>
+      <c r="J101">
+        <v>1</v>
+      </c>
+      <c r="K101">
+        <v>0.5</v>
+      </c>
+      <c r="L101">
+        <v>1</v>
+      </c>
+      <c r="M101">
+        <v>0.5</v>
+      </c>
+      <c r="N101">
+        <v>0.5</v>
+      </c>
+      <c r="O101">
+        <v>1</v>
+      </c>
+      <c r="P101">
+        <v>0.5</v>
+      </c>
+      <c r="Q101">
+        <v>1</v>
+      </c>
+      <c r="R101">
+        <v>0.5</v>
+      </c>
+      <c r="S101">
+        <v>1</v>
+      </c>
+      <c r="T101">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:20">
+      <c r="A102">
+        <v>2000</v>
+      </c>
+      <c r="B102">
+        <v>0.1210075</v>
+      </c>
+      <c r="C102">
+        <v>0.5</v>
+      </c>
+      <c r="D102">
+        <v>0.485</v>
+      </c>
+      <c r="E102">
+        <v>0.6730092637338194</v>
+      </c>
+      <c r="G102">
+        <v>0.998</v>
+      </c>
+      <c r="H102">
+        <v>0.99</v>
+      </c>
+      <c r="I102">
+        <v>1</v>
+      </c>
+      <c r="J102">
+        <v>1</v>
+      </c>
+      <c r="K102">
+        <v>0.5</v>
+      </c>
+      <c r="L102">
+        <v>1</v>
+      </c>
+      <c r="M102">
+        <v>0.5</v>
+      </c>
+      <c r="N102">
+        <v>0.5</v>
+      </c>
+      <c r="O102">
+        <v>1</v>
+      </c>
+      <c r="P102">
+        <v>0.5</v>
+      </c>
+      <c r="Q102">
+        <v>1</v>
+      </c>
+      <c r="R102">
+        <v>0.5</v>
+      </c>
+      <c r="S102">
+        <v>1</v>
+      </c>
+      <c r="T102">
         <v>1</v>
       </c>
     </row>
